--- a/output/graficos_nacionales/plot_nacional_d_enveje_a_2021.xlsx
+++ b/output/graficos_nacionales/plot_nacional_d_enveje_a_2021.xlsx
@@ -16141,7 +16141,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Índice de envejecimiento</t>
+          <t>Por comunas</t>
         </is>
       </c>
     </row>

--- a/output/graficos_nacionales/plot_nacional_d_enveje_a_2021.xlsx
+++ b/output/graficos_nacionales/plot_nacional_d_enveje_a_2021.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="727" uniqueCount="727">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="730" uniqueCount="730">
   <si>
     <t xml:space="preserve">year</t>
   </si>
@@ -133,22 +133,28 @@
     <t xml:space="preserve">Coyhaique</t>
   </si>
   <si>
+    <t xml:space="preserve">11201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aysén</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cisnes</t>
+  </si>
+  <si>
     <t xml:space="preserve">12303</t>
   </si>
   <si>
     <t xml:space="preserve">Timaukel</t>
   </si>
   <si>
-    <t xml:space="preserve">11201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aysén</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cisnes</t>
+    <t xml:space="preserve">11203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Guaitecas</t>
   </si>
   <si>
     <t xml:space="preserve">12402</t>
@@ -157,10 +163,10 @@
     <t xml:space="preserve">Torres del Paine</t>
   </si>
   <si>
-    <t xml:space="preserve">11203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Guaitecas</t>
+    <t xml:space="preserve">11303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tortel</t>
   </si>
   <si>
     <t xml:space="preserve">11302</t>
@@ -169,12 +175,6 @@
     <t xml:space="preserve">O Higgins</t>
   </si>
   <si>
-    <t xml:space="preserve">11303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tortel</t>
-  </si>
-  <si>
     <t xml:space="preserve">12201</t>
   </si>
   <si>
@@ -196,6 +196,15 @@
     <t xml:space="preserve">Macrozona Centro</t>
   </si>
   <si>
+    <t xml:space="preserve">Nuble</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cobquecura</t>
+  </si>
+  <si>
     <t xml:space="preserve">Metropolitana</t>
   </si>
   <si>
@@ -205,15 +214,6 @@
     <t xml:space="preserve">Providencia</t>
   </si>
   <si>
-    <t xml:space="preserve">Nuble</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cobquecura</t>
-  </si>
-  <si>
     <t xml:space="preserve">O'Higgins</t>
   </si>
   <si>
@@ -235,57 +235,57 @@
     <t xml:space="preserve">Ninhue</t>
   </si>
   <si>
+    <t xml:space="preserve">16205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Portezuelo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Las Condes</t>
+  </si>
+  <si>
     <t xml:space="preserve">Valparaiso</t>
   </si>
   <si>
+    <t xml:space="preserve">5604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El Quisco</t>
+  </si>
+  <si>
     <t xml:space="preserve">5605</t>
   </si>
   <si>
     <t xml:space="preserve">El Tabo</t>
   </si>
   <si>
-    <t xml:space="preserve">13114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Las Condes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Portezuelo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El Quisco</t>
-  </si>
-  <si>
     <t xml:space="preserve">7107</t>
   </si>
   <si>
     <t xml:space="preserve">Pencahue</t>
   </si>
   <si>
+    <t xml:space="preserve">5602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Algarrobo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vichuquén</t>
+  </si>
+  <si>
     <t xml:space="preserve">6205</t>
   </si>
   <si>
     <t xml:space="preserve">Navidad</t>
   </si>
   <si>
-    <t xml:space="preserve">5602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Algarrobo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vichuquén</t>
-  </si>
-  <si>
     <t xml:space="preserve">7302</t>
   </si>
   <si>
@@ -310,16 +310,22 @@
     <t xml:space="preserve">Lolol</t>
   </si>
   <si>
+    <t xml:space="preserve">16107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quillón</t>
+  </si>
+  <si>
     <t xml:space="preserve">13120</t>
   </si>
   <si>
     <t xml:space="preserve">Ñuñoa</t>
   </si>
   <si>
-    <t xml:space="preserve">16107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quillón</t>
+    <t xml:space="preserve">16201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quirihue</t>
   </si>
   <si>
     <t xml:space="preserve">7203</t>
@@ -328,10 +334,10 @@
     <t xml:space="preserve">Pelluhue</t>
   </si>
   <si>
-    <t xml:space="preserve">16201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quirihue</t>
+    <t xml:space="preserve">7202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chanco</t>
   </si>
   <si>
     <t xml:space="preserve">5109</t>
@@ -340,22 +346,22 @@
     <t xml:space="preserve">Viña del Mar</t>
   </si>
   <si>
+    <t xml:space="preserve">13113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Reina</t>
+  </si>
+  <si>
     <t xml:space="preserve">16207</t>
   </si>
   <si>
     <t xml:space="preserve">Treguaco</t>
   </si>
   <si>
-    <t xml:space="preserve">13113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La Reina</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chanco</t>
+    <t xml:space="preserve">16203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coelemu</t>
   </si>
   <si>
     <t xml:space="preserve">13121</t>
@@ -364,28 +370,28 @@
     <t xml:space="preserve">Pedro Aguirre Cerda</t>
   </si>
   <si>
-    <t xml:space="preserve">16203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coelemu</t>
-  </si>
-  <si>
     <t xml:space="preserve">16106</t>
   </si>
   <si>
     <t xml:space="preserve">Pinto</t>
   </si>
   <si>
+    <t xml:space="preserve">6307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peralillo</t>
+  </si>
+  <si>
     <t xml:space="preserve">7303</t>
   </si>
   <si>
     <t xml:space="preserve">Licantén</t>
   </si>
   <si>
-    <t xml:space="preserve">6307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Peralillo</t>
+    <t xml:space="preserve">5801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quilpué</t>
   </si>
   <si>
     <t xml:space="preserve">7201</t>
@@ -394,28 +400,28 @@
     <t xml:space="preserve">Cauquenes</t>
   </si>
   <si>
-    <t xml:space="preserve">5801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quilpué</t>
-  </si>
-  <si>
     <t xml:space="preserve">16108</t>
   </si>
   <si>
     <t xml:space="preserve">San Ignacio</t>
   </si>
   <si>
+    <t xml:space="preserve">6306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Palmilla</t>
+  </si>
+  <si>
     <t xml:space="preserve">13118</t>
   </si>
   <si>
     <t xml:space="preserve">Macul</t>
   </si>
   <si>
-    <t xml:space="preserve">6306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Palmilla</t>
+    <t xml:space="preserve">5803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Olmué</t>
   </si>
   <si>
     <t xml:space="preserve">13129</t>
@@ -424,12 +430,6 @@
     <t xml:space="preserve">San Joaquín</t>
   </si>
   <si>
-    <t xml:space="preserve">5803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Olmué</t>
-  </si>
-  <si>
     <t xml:space="preserve">5101</t>
   </si>
   <si>
@@ -448,16 +448,28 @@
     <t xml:space="preserve">Petorca</t>
   </si>
   <si>
+    <t xml:space="preserve">16301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Carlos</t>
+  </si>
+  <si>
     <t xml:space="preserve">7407</t>
   </si>
   <si>
     <t xml:space="preserve">Villa Alegre</t>
   </si>
   <si>
-    <t xml:space="preserve">16301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Carlos</t>
+    <t xml:space="preserve">16305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Nicolás</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Malloa</t>
   </si>
   <si>
     <t xml:space="preserve">6103</t>
@@ -472,12 +484,6 @@
     <t xml:space="preserve">Chépica</t>
   </si>
   <si>
-    <t xml:space="preserve">6109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Malloa</t>
-  </si>
-  <si>
     <t xml:space="preserve">5403</t>
   </si>
   <si>
@@ -490,82 +496,82 @@
     <t xml:space="preserve">Pelarco</t>
   </si>
   <si>
-    <t xml:space="preserve">16305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Nicolás</t>
-  </si>
-  <si>
     <t xml:space="preserve">6113</t>
   </si>
   <si>
     <t xml:space="preserve">Pichidegua</t>
   </si>
   <si>
+    <t xml:space="preserve">16104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El Carmen</t>
+  </si>
+  <si>
     <t xml:space="preserve">13110</t>
   </si>
   <si>
     <t xml:space="preserve">La Florida</t>
   </si>
   <si>
-    <t xml:space="preserve">16104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El Carmen</t>
-  </si>
-  <si>
     <t xml:space="preserve">16102</t>
   </si>
   <si>
     <t xml:space="preserve">Bulnes</t>
   </si>
   <si>
+    <t xml:space="preserve">16105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pemuco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nogales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Fabián</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Litueche</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quillota</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Retiro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Placilla</t>
+  </si>
+  <si>
     <t xml:space="preserve">5405</t>
   </si>
   <si>
     <t xml:space="preserve">Zapallar</t>
   </si>
   <si>
-    <t xml:space="preserve">7405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Retiro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Litueche</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pemuco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Placilla</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nogales</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quillota</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Fabián</t>
+    <t xml:space="preserve">7307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sagrada Familia</t>
   </si>
   <si>
     <t xml:space="preserve">16109</t>
@@ -574,10 +580,10 @@
     <t xml:space="preserve">Yungay</t>
   </si>
   <si>
-    <t xml:space="preserve">7307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sagrada Familia</t>
+    <t xml:space="preserve">7404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parral</t>
   </si>
   <si>
     <t xml:space="preserve">13109</t>
@@ -586,22 +592,22 @@
     <t xml:space="preserve">La Cisterna</t>
   </si>
   <si>
+    <t xml:space="preserve">13131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Ramón</t>
+  </si>
+  <si>
     <t xml:space="preserve">13117</t>
   </si>
   <si>
     <t xml:space="preserve">Lo Prado</t>
   </si>
   <si>
-    <t xml:space="preserve">7404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parral</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Ramón</t>
+    <t xml:space="preserve">6114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quinta de Tilcoco</t>
   </si>
   <si>
     <t xml:space="preserve">13104</t>
@@ -610,22 +616,28 @@
     <t xml:space="preserve">Conchalí</t>
   </si>
   <si>
+    <t xml:space="preserve">6117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Vicente</t>
+  </si>
+  <si>
     <t xml:space="preserve">13111</t>
   </si>
   <si>
     <t xml:space="preserve">La Granja</t>
   </si>
   <si>
-    <t xml:space="preserve">6114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quinta de Tilcoco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Vicente</t>
+    <t xml:space="preserve">7403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Longaví</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rauco</t>
   </si>
   <si>
     <t xml:space="preserve">6112</t>
@@ -640,36 +652,24 @@
     <t xml:space="preserve">Putaendo</t>
   </si>
   <si>
+    <t xml:space="preserve">7108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Río Claro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Ligua</t>
+  </si>
+  <si>
     <t xml:space="preserve">5606</t>
   </si>
   <si>
     <t xml:space="preserve">Santo Domingo</t>
   </si>
   <si>
-    <t xml:space="preserve">5401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La Ligua</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Longaví</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Río Claro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rauco</t>
-  </si>
-  <si>
     <t xml:space="preserve">13403</t>
   </si>
   <si>
@@ -682,18 +682,18 @@
     <t xml:space="preserve">San José de Maipo</t>
   </si>
   <si>
+    <t xml:space="preserve">5103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Concón</t>
+  </si>
+  <si>
     <t xml:space="preserve">7401</t>
   </si>
   <si>
     <t xml:space="preserve">Linares</t>
   </si>
   <si>
-    <t xml:space="preserve">5103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Concón</t>
-  </si>
-  <si>
     <t xml:space="preserve">7308</t>
   </si>
   <si>
@@ -706,24 +706,30 @@
     <t xml:space="preserve">Lo Espejo</t>
   </si>
   <si>
+    <t xml:space="preserve">5601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Antonio</t>
+  </si>
+  <si>
     <t xml:space="preserve">6310</t>
   </si>
   <si>
     <t xml:space="preserve">Santa Cruz</t>
   </si>
   <si>
-    <t xml:space="preserve">5601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Antonio</t>
-  </si>
-  <si>
     <t xml:space="preserve">7110</t>
   </si>
   <si>
     <t xml:space="preserve">San Rafael</t>
   </si>
   <si>
+    <t xml:space="preserve">5105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Puchuncaví</t>
+  </si>
+  <si>
     <t xml:space="preserve">5301</t>
   </si>
   <si>
@@ -736,34 +742,52 @@
     <t xml:space="preserve">Limache</t>
   </si>
   <si>
-    <t xml:space="preserve">5105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Puchuncaví</t>
-  </si>
-  <si>
     <t xml:space="preserve">5804</t>
   </si>
   <si>
     <t xml:space="preserve">Villa Alemana</t>
   </si>
   <si>
+    <t xml:space="preserve">5402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cabildo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Colbún</t>
+  </si>
+  <si>
     <t xml:space="preserve">13126</t>
   </si>
   <si>
     <t xml:space="preserve">Quinta Normal</t>
   </si>
   <si>
-    <t xml:space="preserve">7402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Colbún</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cabildo</t>
+    <t xml:space="preserve">5704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Panquehue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chillán</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Codegua</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Catemu</t>
   </si>
   <si>
     <t xml:space="preserve">13505</t>
@@ -772,10 +796,16 @@
     <t xml:space="preserve">San Pedro</t>
   </si>
   <si>
-    <t xml:space="preserve">5704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Panquehue</t>
+    <t xml:space="preserve">7406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Javier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nancagua</t>
   </si>
   <si>
     <t xml:space="preserve">6201</t>
@@ -784,40 +814,16 @@
     <t xml:space="preserve">Pichilemu</t>
   </si>
   <si>
-    <t xml:space="preserve">16101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chillán</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Javier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Codegua</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Catemu</t>
-  </si>
-  <si>
     <t xml:space="preserve">13105</t>
   </si>
   <si>
     <t xml:space="preserve">El Bosque</t>
   </si>
   <si>
-    <t xml:space="preserve">6305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nancagua</t>
+    <t xml:space="preserve">6107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Las Cabras</t>
   </si>
   <si>
     <t xml:space="preserve">13127</t>
@@ -826,12 +832,6 @@
     <t xml:space="preserve">Recoleta</t>
   </si>
   <si>
-    <t xml:space="preserve">6107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Las Cabras</t>
-  </si>
-  <si>
     <t xml:space="preserve">6104</t>
   </si>
   <si>
@@ -856,28 +856,34 @@
     <t xml:space="preserve">San Clemente</t>
   </si>
   <si>
+    <t xml:space="preserve">13103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cerro Navia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Casablanca</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quintero</t>
+  </si>
+  <si>
     <t xml:space="preserve">5503</t>
   </si>
   <si>
     <t xml:space="preserve">Hijuelas</t>
   </si>
   <si>
-    <t xml:space="preserve">13103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cerro Navia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quintero</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Casablanca</t>
+    <t xml:space="preserve">7408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yerbas Buenas</t>
   </si>
   <si>
     <t xml:space="preserve">13119</t>
@@ -886,12 +892,6 @@
     <t xml:space="preserve">Maipú</t>
   </si>
   <si>
-    <t xml:space="preserve">7408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yerbas Buenas</t>
-  </si>
-  <si>
     <t xml:space="preserve">6303</t>
   </si>
   <si>
@@ -922,70 +922,82 @@
     <t xml:space="preserve">San Miguel</t>
   </si>
   <si>
+    <t xml:space="preserve">6301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Fernando</t>
+  </si>
+  <si>
     <t xml:space="preserve">13503</t>
   </si>
   <si>
     <t xml:space="preserve">Curacaví</t>
   </si>
   <si>
+    <t xml:space="preserve">13102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cerrillos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">María Pinto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coihueco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pirque</t>
+  </si>
+  <si>
     <t xml:space="preserve">13101</t>
   </si>
   <si>
     <t xml:space="preserve">Santiago</t>
   </si>
   <si>
-    <t xml:space="preserve">6301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Fernando</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cerrillos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pirque</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">María Pinto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coihueco</t>
-  </si>
-  <si>
     <t xml:space="preserve">13122</t>
   </si>
   <si>
     <t xml:space="preserve">Peñalolén</t>
   </si>
   <si>
+    <t xml:space="preserve">5304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Esteban</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Doñihue</t>
+  </si>
+  <si>
     <t xml:space="preserve">5701</t>
   </si>
   <si>
     <t xml:space="preserve">San Felipe</t>
   </si>
   <si>
-    <t xml:space="preserve">5304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Esteban</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Doñihue</t>
+    <t xml:space="preserve">6101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rancagua</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Olivar</t>
   </si>
   <si>
     <t xml:space="preserve">13106</t>
@@ -1000,18 +1012,6 @@
     <t xml:space="preserve">Ránquil</t>
   </si>
   <si>
-    <t xml:space="preserve">6101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rancagua</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Olivar</t>
-  </si>
-  <si>
     <t xml:space="preserve">6115</t>
   </si>
   <si>
@@ -1030,18 +1030,18 @@
     <t xml:space="preserve">Curicó</t>
   </si>
   <si>
+    <t xml:space="preserve">7102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Constitución</t>
+  </si>
+  <si>
     <t xml:space="preserve">13501</t>
   </si>
   <si>
     <t xml:space="preserve">Melipilla</t>
   </si>
   <si>
-    <t xml:space="preserve">7102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Constitución</t>
-  </si>
-  <si>
     <t xml:space="preserve">13601</t>
   </si>
   <si>
@@ -1054,18 +1054,18 @@
     <t xml:space="preserve">Independencia</t>
   </si>
   <si>
+    <t xml:space="preserve">13603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Isla de Maipo</t>
+  </si>
+  <si>
     <t xml:space="preserve">5303</t>
   </si>
   <si>
     <t xml:space="preserve">Rinconada</t>
   </si>
   <si>
-    <t xml:space="preserve">13603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Isla de Maipo</t>
-  </si>
-  <si>
     <t xml:space="preserve">6116</t>
   </si>
   <si>
@@ -1084,16 +1084,22 @@
     <t xml:space="preserve">Renca</t>
   </si>
   <si>
+    <t xml:space="preserve">13605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peñaflor</t>
+  </si>
+  <si>
     <t xml:space="preserve">5504</t>
   </si>
   <si>
     <t xml:space="preserve">La Cruz</t>
   </si>
   <si>
-    <t xml:space="preserve">13605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Peñaflor</t>
+    <t xml:space="preserve">13201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Puente Alto</t>
   </si>
   <si>
     <t xml:space="preserve">13602</t>
@@ -1102,10 +1108,10 @@
     <t xml:space="preserve">El Monte</t>
   </si>
   <si>
-    <t xml:space="preserve">13201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Puente Alto</t>
+    <t xml:space="preserve">13404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paine</t>
   </si>
   <si>
     <t xml:space="preserve">13502</t>
@@ -1114,12 +1120,6 @@
     <t xml:space="preserve">Alhué</t>
   </si>
   <si>
-    <t xml:space="preserve">13404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paine</t>
-  </si>
-  <si>
     <t xml:space="preserve">13112</t>
   </si>
   <si>
@@ -1267,21 +1267,21 @@
     <t xml:space="preserve">Punitaqui</t>
   </si>
   <si>
+    <t xml:space="preserve">Arica y Parinacota</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Camarones</t>
+  </si>
+  <si>
     <t xml:space="preserve">4201</t>
   </si>
   <si>
     <t xml:space="preserve">Illapel</t>
   </si>
   <si>
-    <t xml:space="preserve">Arica y Parinacota</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Camarones</t>
-  </si>
-  <si>
     <t xml:space="preserve">4203</t>
   </si>
   <si>
@@ -1318,18 +1318,18 @@
     <t xml:space="preserve">General Lagos</t>
   </si>
   <si>
+    <t xml:space="preserve">15201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Putre</t>
+  </si>
+  <si>
     <t xml:space="preserve">3304</t>
   </si>
   <si>
     <t xml:space="preserve">Huasco</t>
   </si>
   <si>
-    <t xml:space="preserve">15201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Putre</t>
-  </si>
-  <si>
     <t xml:space="preserve">4301</t>
   </si>
   <si>
@@ -1372,16 +1372,22 @@
     <t xml:space="preserve">Pica</t>
   </si>
   <si>
+    <t xml:space="preserve">3102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caldera</t>
+  </si>
+  <si>
     <t xml:space="preserve">1402</t>
   </si>
   <si>
     <t xml:space="preserve">Camiña</t>
   </si>
   <si>
-    <t xml:space="preserve">3102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caldera</t>
+    <t xml:space="preserve">4104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Higuera</t>
   </si>
   <si>
     <t xml:space="preserve">1101</t>
@@ -1393,30 +1399,24 @@
     <t xml:space="preserve">Antofagasta</t>
   </si>
   <si>
+    <t xml:space="preserve">2104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taltal</t>
+  </si>
+  <si>
     <t xml:space="preserve">2301</t>
   </si>
   <si>
     <t xml:space="preserve">Tocopilla</t>
   </si>
   <si>
-    <t xml:space="preserve">4104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La Higuera</t>
-  </si>
-  <si>
     <t xml:space="preserve">15101</t>
   </si>
   <si>
     <t xml:space="preserve">Arica</t>
   </si>
   <si>
-    <t xml:space="preserve">2104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taltal</t>
-  </si>
-  <si>
     <t xml:space="preserve">1403</t>
   </si>
   <si>
@@ -1438,18 +1438,18 @@
     <t xml:space="preserve">Huara</t>
   </si>
   <si>
+    <t xml:space="preserve">3202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diego de Almagro</t>
+  </si>
+  <si>
     <t xml:space="preserve">2302</t>
   </si>
   <si>
     <t xml:space="preserve">María Elena</t>
   </si>
   <si>
-    <t xml:space="preserve">3202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Diego de Almagro</t>
-  </si>
-  <si>
     <t xml:space="preserve">3103</t>
   </si>
   <si>
@@ -1474,18 +1474,18 @@
     <t xml:space="preserve">Mejillones</t>
   </si>
   <si>
+    <t xml:space="preserve">2202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ollagüe</t>
+  </si>
+  <si>
     <t xml:space="preserve">2203</t>
   </si>
   <si>
     <t xml:space="preserve">San Pedro de Atacama</t>
   </si>
   <si>
-    <t xml:space="preserve">2202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ollagüe</t>
-  </si>
-  <si>
     <t xml:space="preserve">1107</t>
   </si>
   <si>
@@ -1528,28 +1528,34 @@
     <t xml:space="preserve">Yumbel</t>
   </si>
   <si>
+    <t xml:space="preserve">10103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cochamó</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8310</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Rosendo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Florida</t>
+  </si>
+  <si>
     <t xml:space="preserve">10108</t>
   </si>
   <si>
     <t xml:space="preserve">Maullín</t>
   </si>
   <si>
-    <t xml:space="preserve">10103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cochamó</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8310</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Rosendo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Florida</t>
+    <t xml:space="preserve">10307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Pablo</t>
   </si>
   <si>
     <t xml:space="preserve">10206</t>
@@ -1558,18 +1564,18 @@
     <t xml:space="preserve">Puqueldón</t>
   </si>
   <si>
-    <t xml:space="preserve">10307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Pablo</t>
-  </si>
-  <si>
     <t xml:space="preserve">8309</t>
   </si>
   <si>
     <t xml:space="preserve">Quilleco</t>
   </si>
   <si>
+    <t xml:space="preserve">10209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quemchi</t>
+  </si>
+  <si>
     <t xml:space="preserve">8302</t>
   </si>
   <si>
@@ -1582,12 +1588,6 @@
     <t xml:space="preserve">Fresia</t>
   </si>
   <si>
-    <t xml:space="preserve">10209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quemchi</t>
-  </si>
-  <si>
     <t xml:space="preserve">La Araucania</t>
   </si>
   <si>
@@ -1597,34 +1597,40 @@
     <t xml:space="preserve">Gorbea</t>
   </si>
   <si>
+    <t xml:space="preserve">10210</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quinchao</t>
+  </si>
+  <si>
     <t xml:space="preserve">9203</t>
   </si>
   <si>
     <t xml:space="preserve">Curacautín</t>
   </si>
   <si>
-    <t xml:space="preserve">10210</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quinchao</t>
-  </si>
-  <si>
     <t xml:space="preserve">10305</t>
   </si>
   <si>
     <t xml:space="preserve">Río Negro</t>
   </si>
   <si>
+    <t xml:space="preserve">10303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Purranque</t>
+  </si>
+  <si>
     <t xml:space="preserve">8101</t>
   </si>
   <si>
     <t xml:space="preserve">Concepción</t>
   </si>
   <si>
-    <t xml:space="preserve">10303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Purranque</t>
+    <t xml:space="preserve">8106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lota</t>
   </si>
   <si>
     <t xml:space="preserve">9117</t>
@@ -1633,60 +1639,54 @@
     <t xml:space="preserve">Teodoro Schmidt</t>
   </si>
   <si>
+    <t xml:space="preserve">8312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tucapel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tomé</t>
+  </si>
+  <si>
     <t xml:space="preserve">10304</t>
   </si>
   <si>
     <t xml:space="preserve">Puyehue</t>
   </si>
   <si>
-    <t xml:space="preserve">8111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tomé</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lota</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tucapel</t>
-  </si>
-  <si>
     <t xml:space="preserve">9118</t>
   </si>
   <si>
     <t xml:space="preserve">Toltén</t>
   </si>
   <si>
+    <t xml:space="preserve">9105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Freire</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8110</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Talcahuano</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9110</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Melipeuco</t>
+  </si>
+  <si>
     <t xml:space="preserve">9103</t>
   </si>
   <si>
     <t xml:space="preserve">Cunco</t>
   </si>
   <si>
-    <t xml:space="preserve">9105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Freire</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8110</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Talcahuano</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9110</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Melipeuco</t>
-  </si>
-  <si>
     <t xml:space="preserve">Los Rios</t>
   </si>
   <si>
@@ -1702,40 +1702,46 @@
     <t xml:space="preserve">Los Muermos</t>
   </si>
   <si>
+    <t xml:space="preserve">9206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Los Sauces</t>
+  </si>
+  <si>
     <t xml:space="preserve">9210</t>
   </si>
   <si>
     <t xml:space="preserve">Traiguén</t>
   </si>
   <si>
-    <t xml:space="preserve">9206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Los Sauces</t>
-  </si>
-  <si>
     <t xml:space="preserve">10202</t>
   </si>
   <si>
     <t xml:space="preserve">Ancud</t>
   </si>
   <si>
+    <t xml:space="preserve">10204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Curaco de Vélez</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Unión</t>
+  </si>
+  <si>
     <t xml:space="preserve">9211</t>
   </si>
   <si>
     <t xml:space="preserve">Victoria</t>
   </si>
   <si>
-    <t xml:space="preserve">10204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Curaco de Vélez</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La Unión</t>
+    <t xml:space="preserve">8204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contulmo</t>
   </si>
   <si>
     <t xml:space="preserve">10404</t>
@@ -1744,18 +1750,18 @@
     <t xml:space="preserve">Palena</t>
   </si>
   <si>
+    <t xml:space="preserve">8112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hualpén</t>
+  </si>
+  <si>
     <t xml:space="preserve">9109</t>
   </si>
   <si>
     <t xml:space="preserve">Loncoche</t>
   </si>
   <si>
-    <t xml:space="preserve">8112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hualpén</t>
-  </si>
-  <si>
     <t xml:space="preserve">9116</t>
   </si>
   <si>
@@ -1768,10 +1774,10 @@
     <t xml:space="preserve">Pitrufquén</t>
   </si>
   <si>
-    <t xml:space="preserve">8204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Contulmo</t>
+    <t xml:space="preserve">10207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Queilén</t>
   </si>
   <si>
     <t xml:space="preserve">8109</t>
@@ -1780,34 +1786,34 @@
     <t xml:space="preserve">Santa Juana</t>
   </si>
   <si>
+    <t xml:space="preserve">8304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Laja</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lumaco</t>
+  </si>
+  <si>
     <t xml:space="preserve">10401</t>
   </si>
   <si>
     <t xml:space="preserve">Chaitén</t>
   </si>
   <si>
-    <t xml:space="preserve">8304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Laja</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Queilén</t>
-  </si>
-  <si>
     <t xml:space="preserve">14203</t>
   </si>
   <si>
     <t xml:space="preserve">Lago Ranco</t>
   </si>
   <si>
-    <t xml:space="preserve">9207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lumaco</t>
+    <t xml:space="preserve">10302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Puerto Octay</t>
   </si>
   <si>
     <t xml:space="preserve">8107</t>
@@ -1816,12 +1822,6 @@
     <t xml:space="preserve">Penco</t>
   </si>
   <si>
-    <t xml:space="preserve">10302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Puerto Octay</t>
-  </si>
-  <si>
     <t xml:space="preserve">9111</t>
   </si>
   <si>
@@ -1834,16 +1834,28 @@
     <t xml:space="preserve">Santa Bárbara</t>
   </si>
   <si>
+    <t xml:space="preserve">8305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mulchén</t>
+  </si>
+  <si>
     <t xml:space="preserve">14105</t>
   </si>
   <si>
     <t xml:space="preserve">Máfil</t>
   </si>
   <si>
-    <t xml:space="preserve">8305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mulchén</t>
+    <t xml:space="preserve">8103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chiguayante</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carahue</t>
   </si>
   <si>
     <t xml:space="preserve">14107</t>
@@ -1852,18 +1864,6 @@
     <t xml:space="preserve">Paillaco</t>
   </si>
   <si>
-    <t xml:space="preserve">8103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chiguayante</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Carahue</t>
-  </si>
-  <si>
     <t xml:space="preserve">9208</t>
   </si>
   <si>
@@ -1882,34 +1882,40 @@
     <t xml:space="preserve">Valdivia</t>
   </si>
   <si>
+    <t xml:space="preserve">10107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Llanquihue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lanco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nacimiento</t>
+  </si>
+  <si>
     <t xml:space="preserve">8307</t>
   </si>
   <si>
     <t xml:space="preserve">Negrete</t>
   </si>
   <si>
-    <t xml:space="preserve">10107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Llanquihue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lanco</t>
-  </si>
-  <si>
     <t xml:space="preserve">9201</t>
   </si>
   <si>
     <t xml:space="preserve">Angol</t>
   </si>
   <si>
-    <t xml:space="preserve">8306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nacimiento</t>
+    <t xml:space="preserve">10102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calbuco</t>
   </si>
   <si>
     <t xml:space="preserve">14104</t>
@@ -1927,30 +1933,24 @@
     <t xml:space="preserve">Osorno</t>
   </si>
   <si>
-    <t xml:space="preserve">10102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Calbuco</t>
-  </si>
-  <si>
     <t xml:space="preserve">8303</t>
   </si>
   <si>
     <t xml:space="preserve">Cabrero</t>
   </si>
   <si>
+    <t xml:space="preserve">14108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Panguipulli</t>
+  </si>
+  <si>
     <t xml:space="preserve">9113</t>
   </si>
   <si>
     <t xml:space="preserve">Perquenco</t>
   </si>
   <si>
-    <t xml:space="preserve">14108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Panguipulli</t>
-  </si>
-  <si>
     <t xml:space="preserve">10203</t>
   </si>
   <si>
@@ -1963,16 +1963,22 @@
     <t xml:space="preserve">Arauco</t>
   </si>
   <si>
+    <t xml:space="preserve">8201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lebu</t>
+  </si>
+  <si>
     <t xml:space="preserve">9101</t>
   </si>
   <si>
     <t xml:space="preserve">Temuco</t>
   </si>
   <si>
-    <t xml:space="preserve">8201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lebu</t>
+    <t xml:space="preserve">9209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Renaico</t>
   </si>
   <si>
     <t xml:space="preserve">9202</t>
@@ -1981,10 +1987,10 @@
     <t xml:space="preserve">Collipulli</t>
   </si>
   <si>
-    <t xml:space="preserve">9209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Renaico</t>
+    <t xml:space="preserve">10105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Frutillar</t>
   </si>
   <si>
     <t xml:space="preserve">9104</t>
@@ -1993,36 +1999,36 @@
     <t xml:space="preserve">Curarrehue</t>
   </si>
   <si>
-    <t xml:space="preserve">10105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Frutillar</t>
-  </si>
-  <si>
     <t xml:space="preserve">8105</t>
   </si>
   <si>
     <t xml:space="preserve">Hualqui</t>
   </si>
   <si>
+    <t xml:space="preserve">10403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hualaihué</t>
+  </si>
+  <si>
     <t xml:space="preserve">9205</t>
   </si>
   <si>
     <t xml:space="preserve">Lonquimay</t>
   </si>
   <si>
-    <t xml:space="preserve">10403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hualaihué</t>
-  </si>
-  <si>
     <t xml:space="preserve">14202</t>
   </si>
   <si>
     <t xml:space="preserve">Futrono</t>
   </si>
   <si>
+    <t xml:space="preserve">8203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cañete</t>
+  </si>
+  <si>
     <t xml:space="preserve">9120</t>
   </si>
   <si>
@@ -2035,10 +2041,10 @@
     <t xml:space="preserve">Cholchol</t>
   </si>
   <si>
-    <t xml:space="preserve">8203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cañete</t>
+    <t xml:space="preserve">8301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Los Ángeles</t>
   </si>
   <si>
     <t xml:space="preserve">9108</t>
@@ -2047,30 +2053,24 @@
     <t xml:space="preserve">Lautaro</t>
   </si>
   <si>
-    <t xml:space="preserve">8301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Los Ángeles</t>
-  </si>
-  <si>
     <t xml:space="preserve">10205</t>
   </si>
   <si>
     <t xml:space="preserve">Dalcahue</t>
   </si>
   <si>
+    <t xml:space="preserve">10201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Castro</t>
+  </si>
+  <si>
     <t xml:space="preserve">10402</t>
   </si>
   <si>
     <t xml:space="preserve">Futaleufú</t>
   </si>
   <si>
-    <t xml:space="preserve">10201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Castro</t>
-  </si>
-  <si>
     <t xml:space="preserve">9119</t>
   </si>
   <si>
@@ -2089,36 +2089,36 @@
     <t xml:space="preserve">Mariquina</t>
   </si>
   <si>
+    <t xml:space="preserve">9115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pucón</t>
+  </si>
+  <si>
     <t xml:space="preserve">9204</t>
   </si>
   <si>
     <t xml:space="preserve">Ercilla</t>
   </si>
   <si>
-    <t xml:space="preserve">9115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pucón</t>
-  </si>
-  <si>
     <t xml:space="preserve">9112</t>
   </si>
   <si>
     <t xml:space="preserve">Padre Las Casas</t>
   </si>
   <si>
+    <t xml:space="preserve">8206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Los Álamos</t>
+  </si>
+  <si>
     <t xml:space="preserve">10109</t>
   </si>
   <si>
     <t xml:space="preserve">Puerto Varas</t>
   </si>
   <si>
-    <t xml:space="preserve">8206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Los Álamos</t>
-  </si>
-  <si>
     <t xml:space="preserve">10101</t>
   </si>
   <si>
@@ -2143,25 +2143,25 @@
     <t xml:space="preserve">Quellón</t>
   </si>
   <si>
+    <t xml:space="preserve">8314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alto Biobío</t>
+  </si>
+  <si>
     <t xml:space="preserve">14204</t>
   </si>
   <si>
     <t xml:space="preserve">Río Bueno</t>
   </si>
   <si>
-    <t xml:space="preserve">8314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alto Biobío</t>
-  </si>
-  <si>
     <t xml:space="preserve">Campo</t>
   </si>
   <si>
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-27 22:00</t>
+    <t xml:space="preserve">2026-09-04 19:41</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -2173,16 +2173,25 @@
     <t xml:space="preserve">Imagen asociada</t>
   </si>
   <si>
-    <t xml:space="preserve"/>
+    <t xml:space="preserve">plot_nacional_d_enveje_a_2021.png</t>
   </si>
   <si>
     <t xml:space="preserve">Indicador</t>
   </si>
   <si>
+    <t xml:space="preserve">Indice de envejecimiento</t>
+  </si>
+  <si>
     <t xml:space="preserve">Unidad territorial</t>
   </si>
   <si>
+    <t xml:space="preserve">Comuna (vista nacional macrozonal)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Año</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021</t>
   </si>
   <si>
     <t xml:space="preserve">variable</t>
@@ -2632,7 +2641,7 @@
         <v>8</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>180</v>
+        <v>196.04</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>8</v>
@@ -2664,7 +2673,7 @@
         <v>8</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>160.71</v>
+        <v>180</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>8</v>
@@ -2696,7 +2705,7 @@
         <v>8</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>146.26</v>
+        <v>155.42</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>8</v>
@@ -2728,7 +2737,7 @@
         <v>8</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>135.51</v>
+        <v>145.8</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>8</v>
@@ -2760,7 +2769,7 @@
         <v>8</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>131.82</v>
+        <v>138.1</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>8</v>
@@ -2792,7 +2801,7 @@
         <v>8</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>120.57</v>
+        <v>130.08</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>8</v>
@@ -2824,7 +2833,7 @@
         <v>8</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>115.61</v>
+        <v>124.86</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>8</v>
@@ -2856,7 +2865,7 @@
         <v>8</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>100.93</v>
+        <v>104.81</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>8</v>
@@ -2888,7 +2897,7 @@
         <v>8</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>95.97</v>
+        <v>103.65</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>8</v>
@@ -2920,7 +2929,7 @@
         <v>8</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>93.84</v>
+        <v>100.9</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>8</v>
@@ -2952,7 +2961,7 @@
         <v>8</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>88</v>
+        <v>91.67</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>8</v>
@@ -2984,7 +2993,7 @@
         <v>8</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>84.42</v>
+        <v>91.07</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>8</v>
@@ -2995,10 +3004,10 @@
         <v>2021</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>38</v>
@@ -3016,7 +3025,7 @@
         <v>8</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>82.61</v>
+        <v>86.65</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>8</v>
@@ -3048,7 +3057,7 @@
         <v>8</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>80.22</v>
+        <v>83.2</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>8</v>
@@ -3059,10 +3068,10 @@
         <v>2021</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>42</v>
@@ -3080,7 +3089,7 @@
         <v>8</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>75.94</v>
+        <v>82.61</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>8</v>
@@ -3091,10 +3100,10 @@
         <v>2021</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>44</v>
@@ -3112,7 +3121,7 @@
         <v>8</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>69.23</v>
+        <v>70.81</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>8</v>
@@ -3123,10 +3132,10 @@
         <v>2021</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>46</v>
@@ -3144,7 +3153,7 @@
         <v>8</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>65.73</v>
+        <v>69.23</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>8</v>
@@ -3176,7 +3185,7 @@
         <v>8</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>47.06</v>
+        <v>50</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>8</v>
@@ -3208,7 +3217,7 @@
         <v>8</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>44.07</v>
+        <v>47.76</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>8</v>
@@ -3240,7 +3249,7 @@
         <v>8</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>34.08</v>
+        <v>37.23</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>8</v>
@@ -3272,7 +3281,7 @@
         <v>8</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>210.28</v>
+        <v>228.21</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>8</v>
@@ -3283,7 +3292,7 @@
         <v>2021</v>
       </c>
       <c r="B23" s="2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>59</v>
@@ -3304,7 +3313,7 @@
         <v>8</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>208.53</v>
+        <v>223.69</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>8</v>
@@ -3315,7 +3324,7 @@
         <v>2021</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>62</v>
@@ -3336,7 +3345,7 @@
         <v>8</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>208.25</v>
+        <v>222.92</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>8</v>
@@ -3368,7 +3377,7 @@
         <v>8</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>195.36</v>
+        <v>208.38</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>8</v>
@@ -3400,7 +3409,7 @@
         <v>8</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>194.92</v>
+        <v>207.16</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>8</v>
@@ -3414,7 +3423,7 @@
         <v>16</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>70</v>
@@ -3432,7 +3441,7 @@
         <v>8</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>183.97</v>
+        <v>200.13</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>8</v>
@@ -3443,17 +3452,17 @@
         <v>2021</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="C28" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D28" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="D28" s="2" t="s">
+      <c r="E28" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="E28" s="2" t="s">
-        <v>74</v>
-      </c>
       <c r="F28" s="2" t="s">
         <v>57</v>
       </c>
@@ -3464,7 +3473,7 @@
         <v>8</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>180.19</v>
+        <v>195.18</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>8</v>
@@ -3478,14 +3487,14 @@
         <v>13</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D29" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E29" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="E29" s="2" t="s">
-        <v>76</v>
-      </c>
       <c r="F29" s="2" t="s">
         <v>57</v>
       </c>
@@ -3496,7 +3505,7 @@
         <v>8</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>178.9</v>
+        <v>193.66</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>8</v>
@@ -3507,10 +3516,10 @@
         <v>2021</v>
       </c>
       <c r="B30" s="2" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>77</v>
@@ -3528,7 +3537,7 @@
         <v>8</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>178.68</v>
+        <v>192.07</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>8</v>
@@ -3542,7 +3551,7 @@
         <v>5</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>79</v>
@@ -3560,7 +3569,7 @@
         <v>8</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>178.53</v>
+        <v>191.91</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>8</v>
@@ -3592,7 +3601,7 @@
         <v>8</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>170.16</v>
+        <v>184.35</v>
       </c>
       <c r="J32" s="2" t="s">
         <v>8</v>
@@ -3603,10 +3612,10 @@
         <v>2021</v>
       </c>
       <c r="B33" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>83</v>
@@ -3624,7 +3633,7 @@
         <v>8</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>169.27</v>
+        <v>182.87</v>
       </c>
       <c r="J33" s="2" t="s">
         <v>8</v>
@@ -3635,10 +3644,10 @@
         <v>2021</v>
       </c>
       <c r="B34" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>85</v>
@@ -3656,7 +3665,7 @@
         <v>8</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>169.04</v>
+        <v>180.46</v>
       </c>
       <c r="J34" s="2" t="s">
         <v>8</v>
@@ -3667,10 +3676,10 @@
         <v>2021</v>
       </c>
       <c r="B35" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>87</v>
@@ -3688,7 +3697,7 @@
         <v>8</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>168.13</v>
+        <v>180.29</v>
       </c>
       <c r="J35" s="2" t="s">
         <v>8</v>
@@ -3720,7 +3729,7 @@
         <v>8</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>166.38</v>
+        <v>180.22</v>
       </c>
       <c r="J36" s="2" t="s">
         <v>8</v>
@@ -3734,7 +3743,7 @@
         <v>13</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>91</v>
@@ -3752,7 +3761,7 @@
         <v>8</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>165.89</v>
+        <v>179.98</v>
       </c>
       <c r="J37" s="2" t="s">
         <v>8</v>
@@ -3784,7 +3793,7 @@
         <v>8</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>165.42</v>
+        <v>177.58</v>
       </c>
       <c r="J38" s="2" t="s">
         <v>8</v>
@@ -3816,7 +3825,7 @@
         <v>8</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>159.67</v>
+        <v>170.41</v>
       </c>
       <c r="J39" s="2" t="s">
         <v>8</v>
@@ -3827,7 +3836,7 @@
         <v>2021</v>
       </c>
       <c r="B40" s="2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>59</v>
@@ -3848,7 +3857,7 @@
         <v>8</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>159.21</v>
+        <v>169.53</v>
       </c>
       <c r="J40" s="2" t="s">
         <v>8</v>
@@ -3859,7 +3868,7 @@
         <v>2021</v>
       </c>
       <c r="B41" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>62</v>
@@ -3880,7 +3889,7 @@
         <v>8</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>157.52</v>
+        <v>169.47</v>
       </c>
       <c r="J41" s="2" t="s">
         <v>8</v>
@@ -3891,10 +3900,10 @@
         <v>2021</v>
       </c>
       <c r="B42" s="2" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>101</v>
@@ -3912,7 +3921,7 @@
         <v>8</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>156.22</v>
+        <v>168.18</v>
       </c>
       <c r="J42" s="2" t="s">
         <v>8</v>
@@ -3923,10 +3932,10 @@
         <v>2021</v>
       </c>
       <c r="B43" s="2" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>103</v>
@@ -3944,7 +3953,7 @@
         <v>8</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>154.15</v>
+        <v>166.89</v>
       </c>
       <c r="J43" s="2" t="s">
         <v>8</v>
@@ -3955,10 +3964,10 @@
         <v>2021</v>
       </c>
       <c r="B44" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>105</v>
@@ -3976,7 +3985,7 @@
         <v>8</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>153.65</v>
+        <v>165.53</v>
       </c>
       <c r="J44" s="2" t="s">
         <v>8</v>
@@ -3987,10 +3996,10 @@
         <v>2021</v>
       </c>
       <c r="B45" s="2" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>107</v>
@@ -4008,7 +4017,7 @@
         <v>8</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>152.9</v>
+        <v>165.13</v>
       </c>
       <c r="J45" s="2" t="s">
         <v>8</v>
@@ -4022,7 +4031,7 @@
         <v>13</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>109</v>
@@ -4040,7 +4049,7 @@
         <v>8</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>152.03</v>
+        <v>164.12</v>
       </c>
       <c r="J46" s="2" t="s">
         <v>8</v>
@@ -4051,10 +4060,10 @@
         <v>2021</v>
       </c>
       <c r="B47" s="2" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>111</v>
@@ -4072,7 +4081,7 @@
         <v>8</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>150.36</v>
+        <v>163.34</v>
       </c>
       <c r="J47" s="2" t="s">
         <v>8</v>
@@ -4083,7 +4092,7 @@
         <v>2021</v>
       </c>
       <c r="B48" s="2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>59</v>
@@ -4104,7 +4113,7 @@
         <v>8</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>149.91</v>
+        <v>161.71</v>
       </c>
       <c r="J48" s="2" t="s">
         <v>8</v>
@@ -4115,7 +4124,7 @@
         <v>2021</v>
       </c>
       <c r="B49" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>62</v>
@@ -4136,7 +4145,7 @@
         <v>8</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>149.85</v>
+        <v>160.79</v>
       </c>
       <c r="J49" s="2" t="s">
         <v>8</v>
@@ -4150,7 +4159,7 @@
         <v>16</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>117</v>
@@ -4168,7 +4177,7 @@
         <v>8</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>146.7</v>
+        <v>157.91</v>
       </c>
       <c r="J50" s="2" t="s">
         <v>8</v>
@@ -4179,10 +4188,10 @@
         <v>2021</v>
       </c>
       <c r="B51" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>119</v>
@@ -4200,7 +4209,7 @@
         <v>8</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>145.64</v>
+        <v>157.09</v>
       </c>
       <c r="J51" s="2" t="s">
         <v>8</v>
@@ -4211,10 +4220,10 @@
         <v>2021</v>
       </c>
       <c r="B52" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>121</v>
@@ -4232,7 +4241,7 @@
         <v>8</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>145.08</v>
+        <v>156.12</v>
       </c>
       <c r="J52" s="2" t="s">
         <v>8</v>
@@ -4243,10 +4252,10 @@
         <v>2021</v>
       </c>
       <c r="B53" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>123</v>
@@ -4264,7 +4273,7 @@
         <v>8</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>144.91</v>
+        <v>156.11</v>
       </c>
       <c r="J53" s="2" t="s">
         <v>8</v>
@@ -4275,10 +4284,10 @@
         <v>2021</v>
       </c>
       <c r="B54" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>125</v>
@@ -4296,7 +4305,7 @@
         <v>8</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>144.79</v>
+        <v>155.99</v>
       </c>
       <c r="J54" s="2" t="s">
         <v>8</v>
@@ -4310,7 +4319,7 @@
         <v>16</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>127</v>
@@ -4328,7 +4337,7 @@
         <v>8</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>144.74</v>
+        <v>155.91</v>
       </c>
       <c r="J55" s="2" t="s">
         <v>8</v>
@@ -4339,10 +4348,10 @@
         <v>2021</v>
       </c>
       <c r="B56" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>129</v>
@@ -4360,7 +4369,7 @@
         <v>8</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>143.79</v>
+        <v>155.45</v>
       </c>
       <c r="J56" s="2" t="s">
         <v>8</v>
@@ -4371,10 +4380,10 @@
         <v>2021</v>
       </c>
       <c r="B57" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>131</v>
@@ -4392,7 +4401,7 @@
         <v>8</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>142.81</v>
+        <v>154.16</v>
       </c>
       <c r="J57" s="2" t="s">
         <v>8</v>
@@ -4403,10 +4412,10 @@
         <v>2021</v>
       </c>
       <c r="B58" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>133</v>
@@ -4424,7 +4433,7 @@
         <v>8</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>142.2</v>
+        <v>152.81</v>
       </c>
       <c r="J58" s="2" t="s">
         <v>8</v>
@@ -4435,10 +4444,10 @@
         <v>2021</v>
       </c>
       <c r="B59" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>135</v>
@@ -4456,7 +4465,7 @@
         <v>8</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>142.18</v>
+        <v>151.86</v>
       </c>
       <c r="J59" s="2" t="s">
         <v>8</v>
@@ -4470,7 +4479,7 @@
         <v>5</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>137</v>
@@ -4488,7 +4497,7 @@
         <v>8</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>140.55</v>
+        <v>151.16</v>
       </c>
       <c r="J60" s="2" t="s">
         <v>8</v>
@@ -4502,7 +4511,7 @@
         <v>5</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>139</v>
@@ -4520,7 +4529,7 @@
         <v>8</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>138.49</v>
+        <v>149.03</v>
       </c>
       <c r="J61" s="2" t="s">
         <v>8</v>
@@ -4534,7 +4543,7 @@
         <v>5</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>141</v>
@@ -4552,7 +4561,7 @@
         <v>8</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>137.65</v>
+        <v>148.02</v>
       </c>
       <c r="J62" s="2" t="s">
         <v>8</v>
@@ -4563,10 +4572,10 @@
         <v>2021</v>
       </c>
       <c r="B63" s="2" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>143</v>
@@ -4584,7 +4593,7 @@
         <v>8</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>136.14</v>
+        <v>147.16</v>
       </c>
       <c r="J63" s="2" t="s">
         <v>8</v>
@@ -4595,10 +4604,10 @@
         <v>2021</v>
       </c>
       <c r="B64" s="2" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>145</v>
@@ -4616,7 +4625,7 @@
         <v>8</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>135.53</v>
+        <v>146.17</v>
       </c>
       <c r="J64" s="2" t="s">
         <v>8</v>
@@ -4627,10 +4636,10 @@
         <v>2021</v>
       </c>
       <c r="B65" s="2" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>147</v>
@@ -4648,7 +4657,7 @@
         <v>8</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>135.02</v>
+        <v>145.97</v>
       </c>
       <c r="J65" s="2" t="s">
         <v>8</v>
@@ -4680,7 +4689,7 @@
         <v>8</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>134.88</v>
+        <v>145.19</v>
       </c>
       <c r="J66" s="2" t="s">
         <v>8</v>
@@ -4712,7 +4721,7 @@
         <v>8</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>134.84</v>
+        <v>144.61</v>
       </c>
       <c r="J67" s="2" t="s">
         <v>8</v>
@@ -4723,10 +4732,10 @@
         <v>2021</v>
       </c>
       <c r="B68" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>153</v>
@@ -4744,7 +4753,7 @@
         <v>8</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>134.27</v>
+        <v>144.44</v>
       </c>
       <c r="J68" s="2" t="s">
         <v>8</v>
@@ -4755,10 +4764,10 @@
         <v>2021</v>
       </c>
       <c r="B69" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>155</v>
@@ -4776,7 +4785,7 @@
         <v>8</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>133.87</v>
+        <v>144.39</v>
       </c>
       <c r="J69" s="2" t="s">
         <v>8</v>
@@ -4787,10 +4796,10 @@
         <v>2021</v>
       </c>
       <c r="B70" s="2" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="D70" s="2" t="s">
         <v>157</v>
@@ -4808,7 +4817,7 @@
         <v>8</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>133.83</v>
+        <v>143.67</v>
       </c>
       <c r="J70" s="2" t="s">
         <v>8</v>
@@ -4840,7 +4849,7 @@
         <v>8</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>133.76</v>
+        <v>143.38</v>
       </c>
       <c r="J71" s="2" t="s">
         <v>8</v>
@@ -4851,7 +4860,7 @@
         <v>2021</v>
       </c>
       <c r="B72" s="2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>59</v>
@@ -4872,7 +4881,7 @@
         <v>8</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>131.92</v>
+        <v>142.47</v>
       </c>
       <c r="J72" s="2" t="s">
         <v>8</v>
@@ -4883,7 +4892,7 @@
         <v>2021</v>
       </c>
       <c r="B73" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>62</v>
@@ -4904,7 +4913,7 @@
         <v>8</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>131.78</v>
+        <v>141.67</v>
       </c>
       <c r="J73" s="2" t="s">
         <v>8</v>
@@ -4918,7 +4927,7 @@
         <v>16</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>165</v>
@@ -4936,7 +4945,7 @@
         <v>8</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>130.38</v>
+        <v>140.99</v>
       </c>
       <c r="J74" s="2" t="s">
         <v>8</v>
@@ -4947,10 +4956,10 @@
         <v>2021</v>
       </c>
       <c r="B75" s="2" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="D75" s="2" t="s">
         <v>167</v>
@@ -4968,7 +4977,7 @@
         <v>8</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>130.16</v>
+        <v>140.39</v>
       </c>
       <c r="J75" s="2" t="s">
         <v>8</v>
@@ -4979,10 +4988,10 @@
         <v>2021</v>
       </c>
       <c r="B76" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="D76" s="2" t="s">
         <v>169</v>
@@ -5000,7 +5009,7 @@
         <v>8</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>129.66</v>
+        <v>139.2</v>
       </c>
       <c r="J76" s="2" t="s">
         <v>8</v>
@@ -5011,10 +5020,10 @@
         <v>2021</v>
       </c>
       <c r="B77" s="2" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D77" s="2" t="s">
         <v>171</v>
@@ -5032,7 +5041,7 @@
         <v>8</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>129.44</v>
+        <v>138.89</v>
       </c>
       <c r="J77" s="2" t="s">
         <v>8</v>
@@ -5043,10 +5052,10 @@
         <v>2021</v>
       </c>
       <c r="B78" s="2" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D78" s="2" t="s">
         <v>173</v>
@@ -5064,7 +5073,7 @@
         <v>8</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>129.4</v>
+        <v>138.73</v>
       </c>
       <c r="J78" s="2" t="s">
         <v>8</v>
@@ -5075,10 +5084,10 @@
         <v>2021</v>
       </c>
       <c r="B79" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="D79" s="2" t="s">
         <v>175</v>
@@ -5096,7 +5105,7 @@
         <v>8</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>129.21</v>
+        <v>138.59</v>
       </c>
       <c r="J79" s="2" t="s">
         <v>8</v>
@@ -5107,10 +5116,10 @@
         <v>2021</v>
       </c>
       <c r="B80" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="D80" s="2" t="s">
         <v>177</v>
@@ -5128,7 +5137,7 @@
         <v>8</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>128.94</v>
+        <v>138.51</v>
       </c>
       <c r="J80" s="2" t="s">
         <v>8</v>
@@ -5139,10 +5148,10 @@
         <v>2021</v>
       </c>
       <c r="B81" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="D81" s="2" t="s">
         <v>179</v>
@@ -5160,7 +5169,7 @@
         <v>8</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>128.49</v>
+        <v>138.48</v>
       </c>
       <c r="J81" s="2" t="s">
         <v>8</v>
@@ -5171,10 +5180,10 @@
         <v>2021</v>
       </c>
       <c r="B82" s="2" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="D82" s="2" t="s">
         <v>181</v>
@@ -5192,7 +5201,7 @@
         <v>8</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>128.49</v>
+        <v>138.42</v>
       </c>
       <c r="J82" s="2" t="s">
         <v>8</v>
@@ -5203,10 +5212,10 @@
         <v>2021</v>
       </c>
       <c r="B83" s="2" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="D83" s="2" t="s">
         <v>183</v>
@@ -5224,7 +5233,7 @@
         <v>8</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>128.33</v>
+        <v>138.11</v>
       </c>
       <c r="J83" s="2" t="s">
         <v>8</v>
@@ -5235,10 +5244,10 @@
         <v>2021</v>
       </c>
       <c r="B84" s="2" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="D84" s="2" t="s">
         <v>185</v>
@@ -5256,7 +5265,7 @@
         <v>8</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>128.28</v>
+        <v>138.04</v>
       </c>
       <c r="J84" s="2" t="s">
         <v>8</v>
@@ -5267,10 +5276,10 @@
         <v>2021</v>
       </c>
       <c r="B85" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="D85" s="2" t="s">
         <v>187</v>
@@ -5288,7 +5297,7 @@
         <v>8</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>128.14</v>
+        <v>137.91</v>
       </c>
       <c r="J85" s="2" t="s">
         <v>8</v>
@@ -5302,7 +5311,7 @@
         <v>13</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D86" s="2" t="s">
         <v>189</v>
@@ -5320,7 +5329,7 @@
         <v>8</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>127.91</v>
+        <v>137.32</v>
       </c>
       <c r="J86" s="2" t="s">
         <v>8</v>
@@ -5331,10 +5340,10 @@
         <v>2021</v>
       </c>
       <c r="B87" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="D87" s="2" t="s">
         <v>191</v>
@@ -5352,7 +5361,7 @@
         <v>8</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>127.77</v>
+        <v>137.06</v>
       </c>
       <c r="J87" s="2" t="s">
         <v>8</v>
@@ -5366,7 +5375,7 @@
         <v>13</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D88" s="2" t="s">
         <v>193</v>
@@ -5384,7 +5393,7 @@
         <v>8</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>127.37</v>
+        <v>137</v>
       </c>
       <c r="J88" s="2" t="s">
         <v>8</v>
@@ -5395,10 +5404,10 @@
         <v>2021</v>
       </c>
       <c r="B89" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="D89" s="2" t="s">
         <v>195</v>
@@ -5416,7 +5425,7 @@
         <v>8</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>127.19</v>
+        <v>136.47</v>
       </c>
       <c r="J89" s="2" t="s">
         <v>8</v>
@@ -5430,7 +5439,7 @@
         <v>13</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D90" s="2" t="s">
         <v>197</v>
@@ -5448,7 +5457,7 @@
         <v>8</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>126.62</v>
+        <v>136.38</v>
       </c>
       <c r="J90" s="2" t="s">
         <v>8</v>
@@ -5480,7 +5489,7 @@
         <v>8</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>126.39</v>
+        <v>136.14</v>
       </c>
       <c r="J91" s="2" t="s">
         <v>8</v>
@@ -5491,10 +5500,10 @@
         <v>2021</v>
       </c>
       <c r="B92" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D92" s="2" t="s">
         <v>201</v>
@@ -5512,7 +5521,7 @@
         <v>8</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>125.92</v>
+        <v>135.83</v>
       </c>
       <c r="J92" s="2" t="s">
         <v>8</v>
@@ -5523,10 +5532,10 @@
         <v>2021</v>
       </c>
       <c r="B93" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="D93" s="2" t="s">
         <v>203</v>
@@ -5544,7 +5553,7 @@
         <v>8</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>125.59</v>
+        <v>134.81</v>
       </c>
       <c r="J93" s="2" t="s">
         <v>8</v>
@@ -5555,10 +5564,10 @@
         <v>2021</v>
       </c>
       <c r="B94" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="D94" s="2" t="s">
         <v>205</v>
@@ -5576,7 +5585,7 @@
         <v>8</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>125.08</v>
+        <v>134.56</v>
       </c>
       <c r="J94" s="2" t="s">
         <v>8</v>
@@ -5587,10 +5596,10 @@
         <v>2021</v>
       </c>
       <c r="B95" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="D95" s="2" t="s">
         <v>207</v>
@@ -5608,7 +5617,7 @@
         <v>8</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>124.55</v>
+        <v>134.18</v>
       </c>
       <c r="J95" s="2" t="s">
         <v>8</v>
@@ -5622,7 +5631,7 @@
         <v>5</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D96" s="2" t="s">
         <v>209</v>
@@ -5640,7 +5649,7 @@
         <v>8</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>124.5</v>
+        <v>133.84</v>
       </c>
       <c r="J96" s="2" t="s">
         <v>8</v>
@@ -5672,7 +5681,7 @@
         <v>8</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>124.43</v>
+        <v>133.39</v>
       </c>
       <c r="J97" s="2" t="s">
         <v>8</v>
@@ -5683,10 +5692,10 @@
         <v>2021</v>
       </c>
       <c r="B98" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="D98" s="2" t="s">
         <v>213</v>
@@ -5704,7 +5713,7 @@
         <v>8</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>124.05</v>
+        <v>132.99</v>
       </c>
       <c r="J98" s="2" t="s">
         <v>8</v>
@@ -5715,10 +5724,10 @@
         <v>2021</v>
       </c>
       <c r="B99" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="D99" s="2" t="s">
         <v>215</v>
@@ -5736,7 +5745,7 @@
         <v>8</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>123.79</v>
+        <v>132.71</v>
       </c>
       <c r="J99" s="2" t="s">
         <v>8</v>
@@ -5750,7 +5759,7 @@
         <v>13</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D100" s="2" t="s">
         <v>217</v>
@@ -5768,7 +5777,7 @@
         <v>8</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>121.5</v>
+        <v>131.16</v>
       </c>
       <c r="J100" s="2" t="s">
         <v>8</v>
@@ -5782,7 +5791,7 @@
         <v>13</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D101" s="2" t="s">
         <v>219</v>
@@ -5800,7 +5809,7 @@
         <v>8</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>121.48</v>
+        <v>130.85</v>
       </c>
       <c r="J101" s="2" t="s">
         <v>8</v>
@@ -5811,10 +5820,10 @@
         <v>2021</v>
       </c>
       <c r="B102" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="D102" s="2" t="s">
         <v>221</v>
@@ -5832,7 +5841,7 @@
         <v>8</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>121.09</v>
+        <v>130.41</v>
       </c>
       <c r="J102" s="2" t="s">
         <v>8</v>
@@ -5843,10 +5852,10 @@
         <v>2021</v>
       </c>
       <c r="B103" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="D103" s="2" t="s">
         <v>223</v>
@@ -5864,7 +5873,7 @@
         <v>8</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>120.98</v>
+        <v>129.82</v>
       </c>
       <c r="J103" s="2" t="s">
         <v>8</v>
@@ -5896,7 +5905,7 @@
         <v>8</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>120.92</v>
+        <v>129.42</v>
       </c>
       <c r="J104" s="2" t="s">
         <v>8</v>
@@ -5910,7 +5919,7 @@
         <v>13</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D105" s="2" t="s">
         <v>227</v>
@@ -5928,7 +5937,7 @@
         <v>8</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>120.72</v>
+        <v>129.04</v>
       </c>
       <c r="J105" s="2" t="s">
         <v>8</v>
@@ -5939,10 +5948,10 @@
         <v>2021</v>
       </c>
       <c r="B106" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="D106" s="2" t="s">
         <v>229</v>
@@ -5960,7 +5969,7 @@
         <v>8</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>119.73</v>
+        <v>129</v>
       </c>
       <c r="J106" s="2" t="s">
         <v>8</v>
@@ -5971,10 +5980,10 @@
         <v>2021</v>
       </c>
       <c r="B107" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="D107" s="2" t="s">
         <v>231</v>
@@ -5992,7 +6001,7 @@
         <v>8</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>119.61</v>
+        <v>128.75</v>
       </c>
       <c r="J107" s="2" t="s">
         <v>8</v>
@@ -6024,7 +6033,7 @@
         <v>8</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>119.35</v>
+        <v>128.68</v>
       </c>
       <c r="J108" s="2" t="s">
         <v>8</v>
@@ -6038,7 +6047,7 @@
         <v>5</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D109" s="2" t="s">
         <v>235</v>
@@ -6056,7 +6065,7 @@
         <v>8</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>119.2</v>
+        <v>128.29</v>
       </c>
       <c r="J109" s="2" t="s">
         <v>8</v>
@@ -6070,7 +6079,7 @@
         <v>5</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D110" s="2" t="s">
         <v>237</v>
@@ -6088,7 +6097,7 @@
         <v>8</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>119.1</v>
+        <v>128.03</v>
       </c>
       <c r="J110" s="2" t="s">
         <v>8</v>
@@ -6102,7 +6111,7 @@
         <v>5</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D111" s="2" t="s">
         <v>239</v>
@@ -6120,7 +6129,7 @@
         <v>8</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>118.92</v>
+        <v>127.73</v>
       </c>
       <c r="J111" s="2" t="s">
         <v>8</v>
@@ -6134,7 +6143,7 @@
         <v>5</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D112" s="2" t="s">
         <v>241</v>
@@ -6152,7 +6161,7 @@
         <v>8</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>118.83</v>
+        <v>127.66</v>
       </c>
       <c r="J112" s="2" t="s">
         <v>8</v>
@@ -6163,10 +6172,10 @@
         <v>2021</v>
       </c>
       <c r="B113" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="D113" s="2" t="s">
         <v>243</v>
@@ -6184,7 +6193,7 @@
         <v>8</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>118.39</v>
+        <v>127.24</v>
       </c>
       <c r="J113" s="2" t="s">
         <v>8</v>
@@ -6216,7 +6225,7 @@
         <v>8</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>117.59</v>
+        <v>127.09</v>
       </c>
       <c r="J114" s="2" t="s">
         <v>8</v>
@@ -6227,10 +6236,10 @@
         <v>2021</v>
       </c>
       <c r="B115" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="D115" s="2" t="s">
         <v>247</v>
@@ -6248,7 +6257,7 @@
         <v>8</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>117.54</v>
+        <v>126.45</v>
       </c>
       <c r="J115" s="2" t="s">
         <v>8</v>
@@ -6259,10 +6268,10 @@
         <v>2021</v>
       </c>
       <c r="B116" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="D116" s="2" t="s">
         <v>249</v>
@@ -6280,7 +6289,7 @@
         <v>8</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>116.51</v>
+        <v>125.64</v>
       </c>
       <c r="J116" s="2" t="s">
         <v>8</v>
@@ -6291,10 +6300,10 @@
         <v>2021</v>
       </c>
       <c r="B117" s="2" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="D117" s="2" t="s">
         <v>251</v>
@@ -6312,7 +6321,7 @@
         <v>8</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>116.32</v>
+        <v>124.89</v>
       </c>
       <c r="J117" s="2" t="s">
         <v>8</v>
@@ -6344,7 +6353,7 @@
         <v>8</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>116.09</v>
+        <v>124.86</v>
       </c>
       <c r="J118" s="2" t="s">
         <v>8</v>
@@ -6355,10 +6364,10 @@
         <v>2021</v>
       </c>
       <c r="B119" s="2" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="D119" s="2" t="s">
         <v>255</v>
@@ -6376,7 +6385,7 @@
         <v>8</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>115.55</v>
+        <v>124.74</v>
       </c>
       <c r="J119" s="2" t="s">
         <v>8</v>
@@ -6387,10 +6396,10 @@
         <v>2021</v>
       </c>
       <c r="B120" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="D120" s="2" t="s">
         <v>257</v>
@@ -6408,7 +6417,7 @@
         <v>8</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>115.54</v>
+        <v>124.62</v>
       </c>
       <c r="J120" s="2" t="s">
         <v>8</v>
@@ -6419,10 +6428,10 @@
         <v>2021</v>
       </c>
       <c r="B121" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="D121" s="2" t="s">
         <v>259</v>
@@ -6440,7 +6449,7 @@
         <v>8</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>115.39</v>
+        <v>124.43</v>
       </c>
       <c r="J121" s="2" t="s">
         <v>8</v>
@@ -6451,10 +6460,10 @@
         <v>2021</v>
       </c>
       <c r="B122" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="D122" s="2" t="s">
         <v>261</v>
@@ -6472,7 +6481,7 @@
         <v>8</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>115.34</v>
+        <v>124.24</v>
       </c>
       <c r="J122" s="2" t="s">
         <v>8</v>
@@ -6483,10 +6492,10 @@
         <v>2021</v>
       </c>
       <c r="B123" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="D123" s="2" t="s">
         <v>263</v>
@@ -6504,7 +6513,7 @@
         <v>8</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>115.04</v>
+        <v>123.53</v>
       </c>
       <c r="J123" s="2" t="s">
         <v>8</v>
@@ -6515,10 +6524,10 @@
         <v>2021</v>
       </c>
       <c r="B124" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D124" s="2" t="s">
         <v>265</v>
@@ -6536,7 +6545,7 @@
         <v>8</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>115.01</v>
+        <v>123.29</v>
       </c>
       <c r="J124" s="2" t="s">
         <v>8</v>
@@ -6547,10 +6556,10 @@
         <v>2021</v>
       </c>
       <c r="B125" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="D125" s="2" t="s">
         <v>267</v>
@@ -6568,7 +6577,7 @@
         <v>8</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>115</v>
+        <v>123.11</v>
       </c>
       <c r="J125" s="2" t="s">
         <v>8</v>
@@ -6579,10 +6588,10 @@
         <v>2021</v>
       </c>
       <c r="B126" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D126" s="2" t="s">
         <v>269</v>
@@ -6600,7 +6609,7 @@
         <v>8</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>114.4</v>
+        <v>122.98</v>
       </c>
       <c r="J126" s="2" t="s">
         <v>8</v>
@@ -6632,7 +6641,7 @@
         <v>8</v>
       </c>
       <c r="I127" s="2" t="n">
-        <v>114.25</v>
+        <v>122.81</v>
       </c>
       <c r="J127" s="2" t="s">
         <v>8</v>
@@ -6664,7 +6673,7 @@
         <v>8</v>
       </c>
       <c r="I128" s="2" t="n">
-        <v>113.26</v>
+        <v>121.85</v>
       </c>
       <c r="J128" s="2" t="s">
         <v>8</v>
@@ -6696,7 +6705,7 @@
         <v>8</v>
       </c>
       <c r="I129" s="2" t="n">
-        <v>112.1</v>
+        <v>120.97</v>
       </c>
       <c r="J129" s="2" t="s">
         <v>8</v>
@@ -6728,7 +6737,7 @@
         <v>8</v>
       </c>
       <c r="I130" s="2" t="n">
-        <v>111.46</v>
+        <v>120.09</v>
       </c>
       <c r="J130" s="2" t="s">
         <v>8</v>
@@ -6739,10 +6748,10 @@
         <v>2021</v>
       </c>
       <c r="B131" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="D131" s="2" t="s">
         <v>279</v>
@@ -6760,7 +6769,7 @@
         <v>8</v>
       </c>
       <c r="I131" s="2" t="n">
-        <v>111.4</v>
+        <v>119.52</v>
       </c>
       <c r="J131" s="2" t="s">
         <v>8</v>
@@ -6771,10 +6780,10 @@
         <v>2021</v>
       </c>
       <c r="B132" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="D132" s="2" t="s">
         <v>281</v>
@@ -6792,7 +6801,7 @@
         <v>8</v>
       </c>
       <c r="I132" s="2" t="n">
-        <v>111.32</v>
+        <v>119.42</v>
       </c>
       <c r="J132" s="2" t="s">
         <v>8</v>
@@ -6806,7 +6815,7 @@
         <v>5</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D133" s="2" t="s">
         <v>283</v>
@@ -6824,7 +6833,7 @@
         <v>8</v>
       </c>
       <c r="I133" s="2" t="n">
-        <v>111.07</v>
+        <v>119.3</v>
       </c>
       <c r="J133" s="2" t="s">
         <v>8</v>
@@ -6838,7 +6847,7 @@
         <v>5</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D134" s="2" t="s">
         <v>285</v>
@@ -6856,7 +6865,7 @@
         <v>8</v>
       </c>
       <c r="I134" s="2" t="n">
-        <v>110.95</v>
+        <v>119.04</v>
       </c>
       <c r="J134" s="2" t="s">
         <v>8</v>
@@ -6867,10 +6876,10 @@
         <v>2021</v>
       </c>
       <c r="B135" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="D135" s="2" t="s">
         <v>287</v>
@@ -6888,7 +6897,7 @@
         <v>8</v>
       </c>
       <c r="I135" s="2" t="n">
-        <v>110.33</v>
+        <v>118.88</v>
       </c>
       <c r="J135" s="2" t="s">
         <v>8</v>
@@ -6899,10 +6908,10 @@
         <v>2021</v>
       </c>
       <c r="B136" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="D136" s="2" t="s">
         <v>289</v>
@@ -6920,7 +6929,7 @@
         <v>8</v>
       </c>
       <c r="I136" s="2" t="n">
-        <v>110.15</v>
+        <v>118.8</v>
       </c>
       <c r="J136" s="2" t="s">
         <v>8</v>
@@ -6952,7 +6961,7 @@
         <v>8</v>
       </c>
       <c r="I137" s="2" t="n">
-        <v>110.12</v>
+        <v>117.96</v>
       </c>
       <c r="J137" s="2" t="s">
         <v>8</v>
@@ -6984,7 +6993,7 @@
         <v>8</v>
       </c>
       <c r="I138" s="2" t="n">
-        <v>109.92</v>
+        <v>117.87</v>
       </c>
       <c r="J138" s="2" t="s">
         <v>8</v>
@@ -7016,7 +7025,7 @@
         <v>8</v>
       </c>
       <c r="I139" s="2" t="n">
-        <v>109.36</v>
+        <v>117.55</v>
       </c>
       <c r="J139" s="2" t="s">
         <v>8</v>
@@ -7030,7 +7039,7 @@
         <v>5</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D140" s="2" t="s">
         <v>297</v>
@@ -7048,7 +7057,7 @@
         <v>8</v>
       </c>
       <c r="I140" s="2" t="n">
-        <v>109.08</v>
+        <v>116.79</v>
       </c>
       <c r="J140" s="2" t="s">
         <v>8</v>
@@ -7062,7 +7071,7 @@
         <v>13</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D141" s="2" t="s">
         <v>299</v>
@@ -7080,7 +7089,7 @@
         <v>8</v>
       </c>
       <c r="I141" s="2" t="n">
-        <v>108.91</v>
+        <v>115.53</v>
       </c>
       <c r="J141" s="2" t="s">
         <v>8</v>
@@ -7091,10 +7100,10 @@
         <v>2021</v>
       </c>
       <c r="B142" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="D142" s="2" t="s">
         <v>301</v>
@@ -7112,7 +7121,7 @@
         <v>8</v>
       </c>
       <c r="I142" s="2" t="n">
-        <v>107.66</v>
+        <v>115.27</v>
       </c>
       <c r="J142" s="2" t="s">
         <v>8</v>
@@ -7126,7 +7135,7 @@
         <v>13</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D143" s="2" t="s">
         <v>303</v>
@@ -7144,7 +7153,7 @@
         <v>8</v>
       </c>
       <c r="I143" s="2" t="n">
-        <v>107.65</v>
+        <v>114.87</v>
       </c>
       <c r="J143" s="2" t="s">
         <v>8</v>
@@ -7155,10 +7164,10 @@
         <v>2021</v>
       </c>
       <c r="B144" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D144" s="2" t="s">
         <v>305</v>
@@ -7176,7 +7185,7 @@
         <v>8</v>
       </c>
       <c r="I144" s="2" t="n">
-        <v>107.5</v>
+        <v>114.54</v>
       </c>
       <c r="J144" s="2" t="s">
         <v>8</v>
@@ -7190,7 +7199,7 @@
         <v>13</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D145" s="2" t="s">
         <v>307</v>
@@ -7208,7 +7217,7 @@
         <v>8</v>
       </c>
       <c r="I145" s="2" t="n">
-        <v>106.66</v>
+        <v>114.41</v>
       </c>
       <c r="J145" s="2" t="s">
         <v>8</v>
@@ -7219,7 +7228,7 @@
         <v>2021</v>
       </c>
       <c r="B146" s="2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C146" s="2" t="s">
         <v>59</v>
@@ -7240,7 +7249,7 @@
         <v>8</v>
       </c>
       <c r="I146" s="2" t="n">
-        <v>106.63</v>
+        <v>114.09</v>
       </c>
       <c r="J146" s="2" t="s">
         <v>8</v>
@@ -7254,7 +7263,7 @@
         <v>13</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D147" s="2" t="s">
         <v>311</v>
@@ -7272,7 +7281,7 @@
         <v>8</v>
       </c>
       <c r="I147" s="2" t="n">
-        <v>106.58</v>
+        <v>114.02</v>
       </c>
       <c r="J147" s="2" t="s">
         <v>8</v>
@@ -7283,7 +7292,7 @@
         <v>2021</v>
       </c>
       <c r="B148" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C148" s="2" t="s">
         <v>62</v>
@@ -7304,7 +7313,7 @@
         <v>8</v>
       </c>
       <c r="I148" s="2" t="n">
-        <v>105.29</v>
+        <v>113.39</v>
       </c>
       <c r="J148" s="2" t="s">
         <v>8</v>
@@ -7318,7 +7327,7 @@
         <v>13</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D149" s="2" t="s">
         <v>315</v>
@@ -7336,7 +7345,7 @@
         <v>8</v>
       </c>
       <c r="I149" s="2" t="n">
-        <v>104.07</v>
+        <v>112.63</v>
       </c>
       <c r="J149" s="2" t="s">
         <v>8</v>
@@ -7350,7 +7359,7 @@
         <v>5</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D150" s="2" t="s">
         <v>317</v>
@@ -7368,7 +7377,7 @@
         <v>8</v>
       </c>
       <c r="I150" s="2" t="n">
-        <v>103.07</v>
+        <v>111.23</v>
       </c>
       <c r="J150" s="2" t="s">
         <v>8</v>
@@ -7379,10 +7388,10 @@
         <v>2021</v>
       </c>
       <c r="B151" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="D151" s="2" t="s">
         <v>319</v>
@@ -7400,7 +7409,7 @@
         <v>8</v>
       </c>
       <c r="I151" s="2" t="n">
-        <v>103.03</v>
+        <v>110.77</v>
       </c>
       <c r="J151" s="2" t="s">
         <v>8</v>
@@ -7411,10 +7420,10 @@
         <v>2021</v>
       </c>
       <c r="B152" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="D152" s="2" t="s">
         <v>321</v>
@@ -7432,7 +7441,7 @@
         <v>8</v>
       </c>
       <c r="I152" s="2" t="n">
-        <v>102.95</v>
+        <v>110.48</v>
       </c>
       <c r="J152" s="2" t="s">
         <v>8</v>
@@ -7443,10 +7452,10 @@
         <v>2021</v>
       </c>
       <c r="B153" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="D153" s="2" t="s">
         <v>323</v>
@@ -7464,7 +7473,7 @@
         <v>8</v>
       </c>
       <c r="I153" s="2" t="n">
-        <v>102.83</v>
+        <v>110.36</v>
       </c>
       <c r="J153" s="2" t="s">
         <v>8</v>
@@ -7475,10 +7484,10 @@
         <v>2021</v>
       </c>
       <c r="B154" s="2" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D154" s="2" t="s">
         <v>325</v>
@@ -7496,7 +7505,7 @@
         <v>8</v>
       </c>
       <c r="I154" s="2" t="n">
-        <v>102.68</v>
+        <v>109.29</v>
       </c>
       <c r="J154" s="2" t="s">
         <v>8</v>
@@ -7507,10 +7516,10 @@
         <v>2021</v>
       </c>
       <c r="B155" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D155" s="2" t="s">
         <v>327</v>
@@ -7528,7 +7537,7 @@
         <v>8</v>
       </c>
       <c r="I155" s="2" t="n">
-        <v>102.6</v>
+        <v>108.95</v>
       </c>
       <c r="J155" s="2" t="s">
         <v>8</v>
@@ -7539,10 +7548,10 @@
         <v>2021</v>
       </c>
       <c r="B156" s="2" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D156" s="2" t="s">
         <v>329</v>
@@ -7560,7 +7569,7 @@
         <v>8</v>
       </c>
       <c r="I156" s="2" t="n">
-        <v>101.21</v>
+        <v>108.49</v>
       </c>
       <c r="J156" s="2" t="s">
         <v>8</v>
@@ -7592,7 +7601,7 @@
         <v>8</v>
       </c>
       <c r="I157" s="2" t="n">
-        <v>100.28</v>
+        <v>107.82</v>
       </c>
       <c r="J157" s="2" t="s">
         <v>8</v>
@@ -7624,7 +7633,7 @@
         <v>8</v>
       </c>
       <c r="I158" s="2" t="n">
-        <v>99.65</v>
+        <v>107.05</v>
       </c>
       <c r="J158" s="2" t="s">
         <v>8</v>
@@ -7656,7 +7665,7 @@
         <v>8</v>
       </c>
       <c r="I159" s="2" t="n">
-        <v>98.85</v>
+        <v>106.22</v>
       </c>
       <c r="J159" s="2" t="s">
         <v>8</v>
@@ -7667,10 +7676,10 @@
         <v>2021</v>
       </c>
       <c r="B160" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="D160" s="2" t="s">
         <v>337</v>
@@ -7688,7 +7697,7 @@
         <v>8</v>
       </c>
       <c r="I160" s="2" t="n">
-        <v>97.56</v>
+        <v>104.86</v>
       </c>
       <c r="J160" s="2" t="s">
         <v>8</v>
@@ -7699,10 +7708,10 @@
         <v>2021</v>
       </c>
       <c r="B161" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="D161" s="2" t="s">
         <v>339</v>
@@ -7720,7 +7729,7 @@
         <v>8</v>
       </c>
       <c r="I161" s="2" t="n">
-        <v>97.08</v>
+        <v>103.96</v>
       </c>
       <c r="J161" s="2" t="s">
         <v>8</v>
@@ -7734,7 +7743,7 @@
         <v>13</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D162" s="2" t="s">
         <v>341</v>
@@ -7752,7 +7761,7 @@
         <v>8</v>
       </c>
       <c r="I162" s="2" t="n">
-        <v>96.52</v>
+        <v>103.88</v>
       </c>
       <c r="J162" s="2" t="s">
         <v>8</v>
@@ -7766,7 +7775,7 @@
         <v>13</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D163" s="2" t="s">
         <v>343</v>
@@ -7784,7 +7793,7 @@
         <v>8</v>
       </c>
       <c r="I163" s="2" t="n">
-        <v>94.92</v>
+        <v>100.28</v>
       </c>
       <c r="J163" s="2" t="s">
         <v>8</v>
@@ -7795,10 +7804,10 @@
         <v>2021</v>
       </c>
       <c r="B164" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="D164" s="2" t="s">
         <v>345</v>
@@ -7816,7 +7825,7 @@
         <v>8</v>
       </c>
       <c r="I164" s="2" t="n">
-        <v>93.48</v>
+        <v>99.91</v>
       </c>
       <c r="J164" s="2" t="s">
         <v>8</v>
@@ -7827,10 +7836,10 @@
         <v>2021</v>
       </c>
       <c r="B165" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="D165" s="2" t="s">
         <v>347</v>
@@ -7848,7 +7857,7 @@
         <v>8</v>
       </c>
       <c r="I165" s="2" t="n">
-        <v>93.09</v>
+        <v>99.66</v>
       </c>
       <c r="J165" s="2" t="s">
         <v>8</v>
@@ -7880,7 +7889,7 @@
         <v>8</v>
       </c>
       <c r="I166" s="2" t="n">
-        <v>92.31</v>
+        <v>99.33</v>
       </c>
       <c r="J166" s="2" t="s">
         <v>8</v>
@@ -7894,7 +7903,7 @@
         <v>13</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D167" s="2" t="s">
         <v>351</v>
@@ -7912,7 +7921,7 @@
         <v>8</v>
       </c>
       <c r="I167" s="2" t="n">
-        <v>90.82</v>
+        <v>97.75</v>
       </c>
       <c r="J167" s="2" t="s">
         <v>8</v>
@@ -7926,7 +7935,7 @@
         <v>13</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D168" s="2" t="s">
         <v>353</v>
@@ -7944,7 +7953,7 @@
         <v>8</v>
       </c>
       <c r="I168" s="2" t="n">
-        <v>90.67</v>
+        <v>97.64</v>
       </c>
       <c r="J168" s="2" t="s">
         <v>8</v>
@@ -7955,10 +7964,10 @@
         <v>2021</v>
       </c>
       <c r="B169" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="D169" s="2" t="s">
         <v>355</v>
@@ -7976,7 +7985,7 @@
         <v>8</v>
       </c>
       <c r="I169" s="2" t="n">
-        <v>90.36</v>
+        <v>97.11</v>
       </c>
       <c r="J169" s="2" t="s">
         <v>8</v>
@@ -7987,10 +7996,10 @@
         <v>2021</v>
       </c>
       <c r="B170" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="D170" s="2" t="s">
         <v>357</v>
@@ -8008,7 +8017,7 @@
         <v>8</v>
       </c>
       <c r="I170" s="2" t="n">
-        <v>90.13</v>
+        <v>96.4</v>
       </c>
       <c r="J170" s="2" t="s">
         <v>8</v>
@@ -8022,7 +8031,7 @@
         <v>13</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D171" s="2" t="s">
         <v>359</v>
@@ -8040,7 +8049,7 @@
         <v>8</v>
       </c>
       <c r="I171" s="2" t="n">
-        <v>89.22</v>
+        <v>95.57</v>
       </c>
       <c r="J171" s="2" t="s">
         <v>8</v>
@@ -8054,7 +8063,7 @@
         <v>13</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D172" s="2" t="s">
         <v>361</v>
@@ -8072,7 +8081,7 @@
         <v>8</v>
       </c>
       <c r="I172" s="2" t="n">
-        <v>88.88</v>
+        <v>95.45</v>
       </c>
       <c r="J172" s="2" t="s">
         <v>8</v>
@@ -8086,7 +8095,7 @@
         <v>13</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D173" s="2" t="s">
         <v>363</v>
@@ -8104,7 +8113,7 @@
         <v>8</v>
       </c>
       <c r="I173" s="2" t="n">
-        <v>88.33</v>
+        <v>94.42</v>
       </c>
       <c r="J173" s="2" t="s">
         <v>8</v>
@@ -8118,7 +8127,7 @@
         <v>13</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D174" s="2" t="s">
         <v>365</v>
@@ -8136,7 +8145,7 @@
         <v>8</v>
       </c>
       <c r="I174" s="2" t="n">
-        <v>87.84</v>
+        <v>93.69</v>
       </c>
       <c r="J174" s="2" t="s">
         <v>8</v>
@@ -8150,7 +8159,7 @@
         <v>13</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D175" s="2" t="s">
         <v>367</v>
@@ -8168,7 +8177,7 @@
         <v>8</v>
       </c>
       <c r="I175" s="2" t="n">
-        <v>86.27</v>
+        <v>92.95</v>
       </c>
       <c r="J175" s="2" t="s">
         <v>8</v>
@@ -8182,7 +8191,7 @@
         <v>16</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D176" s="2" t="s">
         <v>369</v>
@@ -8200,7 +8209,7 @@
         <v>8</v>
       </c>
       <c r="I176" s="2" t="n">
-        <v>85.39</v>
+        <v>91.64</v>
       </c>
       <c r="J176" s="2" t="s">
         <v>8</v>
@@ -8232,7 +8241,7 @@
         <v>8</v>
       </c>
       <c r="I177" s="2" t="n">
-        <v>83.64</v>
+        <v>89.72</v>
       </c>
       <c r="J177" s="2" t="s">
         <v>8</v>
@@ -8246,7 +8255,7 @@
         <v>5</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D178" s="2" t="s">
         <v>373</v>
@@ -8264,7 +8273,7 @@
         <v>8</v>
       </c>
       <c r="I178" s="2" t="n">
-        <v>83.07</v>
+        <v>88.94</v>
       </c>
       <c r="J178" s="2" t="s">
         <v>8</v>
@@ -8278,7 +8287,7 @@
         <v>13</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D179" s="2" t="s">
         <v>375</v>
@@ -8296,7 +8305,7 @@
         <v>8</v>
       </c>
       <c r="I179" s="2" t="n">
-        <v>82.59</v>
+        <v>88.88</v>
       </c>
       <c r="J179" s="2" t="s">
         <v>8</v>
@@ -8310,7 +8319,7 @@
         <v>13</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D180" s="2" t="s">
         <v>377</v>
@@ -8328,7 +8337,7 @@
         <v>8</v>
       </c>
       <c r="I180" s="2" t="n">
-        <v>79.3</v>
+        <v>86.81</v>
       </c>
       <c r="J180" s="2" t="s">
         <v>8</v>
@@ -8342,7 +8351,7 @@
         <v>13</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D181" s="2" t="s">
         <v>379</v>
@@ -8360,7 +8369,7 @@
         <v>8</v>
       </c>
       <c r="I181" s="2" t="n">
-        <v>76.46</v>
+        <v>82.5</v>
       </c>
       <c r="J181" s="2" t="s">
         <v>8</v>
@@ -8374,7 +8383,7 @@
         <v>5</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D182" s="2" t="s">
         <v>381</v>
@@ -8392,7 +8401,7 @@
         <v>8</v>
       </c>
       <c r="I182" s="2" t="n">
-        <v>75.35</v>
+        <v>78.92</v>
       </c>
       <c r="J182" s="2" t="s">
         <v>8</v>
@@ -8406,7 +8415,7 @@
         <v>16</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D183" s="2" t="s">
         <v>383</v>
@@ -8424,7 +8433,7 @@
         <v>8</v>
       </c>
       <c r="I183" s="2" t="n">
-        <v>73.36</v>
+        <v>76.77</v>
       </c>
       <c r="J183" s="2" t="s">
         <v>8</v>
@@ -8438,7 +8447,7 @@
         <v>13</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D184" s="2" t="s">
         <v>385</v>
@@ -8456,7 +8465,7 @@
         <v>8</v>
       </c>
       <c r="I184" s="2" t="n">
-        <v>71.27</v>
+        <v>76.22</v>
       </c>
       <c r="J184" s="2" t="s">
         <v>8</v>
@@ -8470,7 +8479,7 @@
         <v>13</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D185" s="2" t="s">
         <v>387</v>
@@ -8488,7 +8497,7 @@
         <v>8</v>
       </c>
       <c r="I185" s="2" t="n">
-        <v>69.39</v>
+        <v>73.79</v>
       </c>
       <c r="J185" s="2" t="s">
         <v>8</v>
@@ -8520,7 +8529,7 @@
         <v>8</v>
       </c>
       <c r="I186" s="2" t="n">
-        <v>67.9</v>
+        <v>72.8</v>
       </c>
       <c r="J186" s="2" t="s">
         <v>8</v>
@@ -8534,7 +8543,7 @@
         <v>13</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D187" s="2" t="s">
         <v>391</v>
@@ -8552,7 +8561,7 @@
         <v>8</v>
       </c>
       <c r="I187" s="2" t="n">
-        <v>61.37</v>
+        <v>65.99</v>
       </c>
       <c r="J187" s="2" t="s">
         <v>8</v>
@@ -8566,7 +8575,7 @@
         <v>5</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D188" s="2" t="s">
         <v>393</v>
@@ -8584,7 +8593,7 @@
         <v>8</v>
       </c>
       <c r="I188" s="2" t="n">
-        <v>57.84</v>
+        <v>60.09</v>
       </c>
       <c r="J188" s="2" t="s">
         <v>8</v>
@@ -8616,7 +8625,7 @@
         <v>8</v>
       </c>
       <c r="I189" s="2" t="n">
-        <v>52.81</v>
+        <v>56.4</v>
       </c>
       <c r="J189" s="2" t="s">
         <v>8</v>
@@ -8630,7 +8639,7 @@
         <v>13</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D190" s="2" t="s">
         <v>396</v>
@@ -8648,7 +8657,7 @@
         <v>8</v>
       </c>
       <c r="I190" s="2" t="n">
-        <v>48.7</v>
+        <v>52.1</v>
       </c>
       <c r="J190" s="2" t="s">
         <v>8</v>
@@ -8662,7 +8671,7 @@
         <v>13</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D191" s="2" t="s">
         <v>398</v>
@@ -8680,7 +8689,7 @@
         <v>8</v>
       </c>
       <c r="I191" s="2" t="n">
-        <v>48.66</v>
+        <v>50.47</v>
       </c>
       <c r="J191" s="2" t="s">
         <v>8</v>
@@ -8694,7 +8703,7 @@
         <v>13</v>
       </c>
       <c r="C192" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D192" s="2" t="s">
         <v>400</v>
@@ -8712,7 +8721,7 @@
         <v>8</v>
       </c>
       <c r="I192" s="2" t="n">
-        <v>44.2</v>
+        <v>47.13</v>
       </c>
       <c r="J192" s="2" t="s">
         <v>8</v>
@@ -8744,7 +8753,7 @@
         <v>8</v>
       </c>
       <c r="I193" s="2" t="n">
-        <v>179.61</v>
+        <v>198.01</v>
       </c>
       <c r="J193" s="2" t="s">
         <v>8</v>
@@ -8776,7 +8785,7 @@
         <v>8</v>
       </c>
       <c r="I194" s="2" t="n">
-        <v>174.3</v>
+        <v>189.72</v>
       </c>
       <c r="J194" s="2" t="s">
         <v>8</v>
@@ -8808,7 +8817,7 @@
         <v>8</v>
       </c>
       <c r="I195" s="2" t="n">
-        <v>164.56</v>
+        <v>177.54</v>
       </c>
       <c r="J195" s="2" t="s">
         <v>8</v>
@@ -8840,7 +8849,7 @@
         <v>8</v>
       </c>
       <c r="I196" s="2" t="n">
-        <v>135.54</v>
+        <v>145.84</v>
       </c>
       <c r="J196" s="2" t="s">
         <v>8</v>
@@ -8872,7 +8881,7 @@
         <v>8</v>
       </c>
       <c r="I197" s="2" t="n">
-        <v>124.49</v>
+        <v>134.93</v>
       </c>
       <c r="J197" s="2" t="s">
         <v>8</v>
@@ -8883,16 +8892,16 @@
         <v>2021</v>
       </c>
       <c r="B198" s="2" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="C198" s="2" t="s">
-        <v>402</v>
+        <v>416</v>
       </c>
       <c r="D198" s="2" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="E198" s="2" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="F198" s="2" t="s">
         <v>405</v>
@@ -8904,7 +8913,7 @@
         <v>8</v>
       </c>
       <c r="I198" s="2" t="n">
-        <v>120.95</v>
+        <v>134.33</v>
       </c>
       <c r="J198" s="2" t="s">
         <v>8</v>
@@ -8915,10 +8924,10 @@
         <v>2021</v>
       </c>
       <c r="B199" s="2" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="C199" s="2" t="s">
-        <v>418</v>
+        <v>402</v>
       </c>
       <c r="D199" s="2" t="s">
         <v>419</v>
@@ -8936,7 +8945,7 @@
         <v>8</v>
       </c>
       <c r="I199" s="2" t="n">
-        <v>120</v>
+        <v>130.31</v>
       </c>
       <c r="J199" s="2" t="s">
         <v>8</v>
@@ -8968,7 +8977,7 @@
         <v>8</v>
       </c>
       <c r="I200" s="2" t="n">
-        <v>118.91</v>
+        <v>127.69</v>
       </c>
       <c r="J200" s="2" t="s">
         <v>8</v>
@@ -9000,7 +9009,7 @@
         <v>8</v>
       </c>
       <c r="I201" s="2" t="n">
-        <v>113.77</v>
+        <v>122.34</v>
       </c>
       <c r="J201" s="2" t="s">
         <v>8</v>
@@ -9032,7 +9041,7 @@
         <v>8</v>
       </c>
       <c r="I202" s="2" t="n">
-        <v>112.35</v>
+        <v>120.7</v>
       </c>
       <c r="J202" s="2" t="s">
         <v>8</v>
@@ -9064,7 +9073,7 @@
         <v>8</v>
       </c>
       <c r="I203" s="2" t="n">
-        <v>111.47</v>
+        <v>119.61</v>
       </c>
       <c r="J203" s="2" t="s">
         <v>8</v>
@@ -9096,7 +9105,7 @@
         <v>8</v>
       </c>
       <c r="I204" s="2" t="n">
-        <v>110.42</v>
+        <v>117.95</v>
       </c>
       <c r="J204" s="2" t="s">
         <v>8</v>
@@ -9110,7 +9119,7 @@
         <v>15</v>
       </c>
       <c r="C205" s="2" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="D205" s="2" t="s">
         <v>431</v>
@@ -9128,7 +9137,7 @@
         <v>8</v>
       </c>
       <c r="I205" s="2" t="n">
-        <v>108.05</v>
+        <v>116.05</v>
       </c>
       <c r="J205" s="2" t="s">
         <v>8</v>
@@ -9139,10 +9148,10 @@
         <v>2021</v>
       </c>
       <c r="B206" s="2" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="C206" s="2" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="D206" s="2" t="s">
         <v>433</v>
@@ -9160,7 +9169,7 @@
         <v>8</v>
       </c>
       <c r="I206" s="2" t="n">
-        <v>106.07</v>
+        <v>115.2</v>
       </c>
       <c r="J206" s="2" t="s">
         <v>8</v>
@@ -9171,10 +9180,10 @@
         <v>2021</v>
       </c>
       <c r="B207" s="2" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="C207" s="2" t="s">
-        <v>418</v>
+        <v>411</v>
       </c>
       <c r="D207" s="2" t="s">
         <v>435</v>
@@ -9192,7 +9201,7 @@
         <v>8</v>
       </c>
       <c r="I207" s="2" t="n">
-        <v>103.97</v>
+        <v>112.46</v>
       </c>
       <c r="J207" s="2" t="s">
         <v>8</v>
@@ -9224,7 +9233,7 @@
         <v>8</v>
       </c>
       <c r="I208" s="2" t="n">
-        <v>103.95</v>
+        <v>111.89</v>
       </c>
       <c r="J208" s="2" t="s">
         <v>8</v>
@@ -9256,7 +9265,7 @@
         <v>8</v>
       </c>
       <c r="I209" s="2" t="n">
-        <v>101.44</v>
+        <v>109.34</v>
       </c>
       <c r="J209" s="2" t="s">
         <v>8</v>
@@ -9288,7 +9297,7 @@
         <v>8</v>
       </c>
       <c r="I210" s="2" t="n">
-        <v>97.63</v>
+        <v>105.1</v>
       </c>
       <c r="J210" s="2" t="s">
         <v>8</v>
@@ -9320,7 +9329,7 @@
         <v>8</v>
       </c>
       <c r="I211" s="2" t="n">
-        <v>97.13</v>
+        <v>104.4</v>
       </c>
       <c r="J211" s="2" t="s">
         <v>8</v>
@@ -9352,7 +9361,7 @@
         <v>8</v>
       </c>
       <c r="I212" s="2" t="n">
-        <v>96.44</v>
+        <v>103.77</v>
       </c>
       <c r="J212" s="2" t="s">
         <v>8</v>
@@ -9384,7 +9393,7 @@
         <v>8</v>
       </c>
       <c r="I213" s="2" t="n">
-        <v>93.02</v>
+        <v>99.69</v>
       </c>
       <c r="J213" s="2" t="s">
         <v>8</v>
@@ -9416,7 +9425,7 @@
         <v>8</v>
       </c>
       <c r="I214" s="2" t="n">
-        <v>92.91</v>
+        <v>99.54</v>
       </c>
       <c r="J214" s="2" t="s">
         <v>8</v>
@@ -9427,10 +9436,10 @@
         <v>2021</v>
       </c>
       <c r="B215" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C215" s="2" t="s">
-        <v>448</v>
+        <v>411</v>
       </c>
       <c r="D215" s="2" t="s">
         <v>451</v>
@@ -9448,7 +9457,7 @@
         <v>8</v>
       </c>
       <c r="I215" s="2" t="n">
-        <v>92.31</v>
+        <v>99.54</v>
       </c>
       <c r="J215" s="2" t="s">
         <v>8</v>
@@ -9459,10 +9468,10 @@
         <v>2021</v>
       </c>
       <c r="B216" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C216" s="2" t="s">
-        <v>411</v>
+        <v>448</v>
       </c>
       <c r="D216" s="2" t="s">
         <v>453</v>
@@ -9480,7 +9489,7 @@
         <v>8</v>
       </c>
       <c r="I216" s="2" t="n">
-        <v>92.18</v>
+        <v>98.77</v>
       </c>
       <c r="J216" s="2" t="s">
         <v>8</v>
@@ -9491,10 +9500,10 @@
         <v>2021</v>
       </c>
       <c r="B217" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C217" s="2" t="s">
-        <v>448</v>
+        <v>402</v>
       </c>
       <c r="D217" s="2" t="s">
         <v>455</v>
@@ -9512,7 +9521,7 @@
         <v>8</v>
       </c>
       <c r="I217" s="2" t="n">
-        <v>91.18</v>
+        <v>98.59</v>
       </c>
       <c r="J217" s="2" t="s">
         <v>8</v>
@@ -9523,16 +9532,16 @@
         <v>2021</v>
       </c>
       <c r="B218" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C218" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="D218" s="2" t="s">
         <v>457</v>
       </c>
-      <c r="D218" s="2" t="s">
+      <c r="E218" s="2" t="s">
         <v>458</v>
-      </c>
-      <c r="E218" s="2" t="s">
-        <v>459</v>
       </c>
       <c r="F218" s="2" t="s">
         <v>405</v>
@@ -9544,7 +9553,7 @@
         <v>8</v>
       </c>
       <c r="I218" s="2" t="n">
-        <v>90.25</v>
+        <v>97.61</v>
       </c>
       <c r="J218" s="2" t="s">
         <v>8</v>
@@ -9555,10 +9564,10 @@
         <v>2021</v>
       </c>
       <c r="B219" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C219" s="2" t="s">
-        <v>402</v>
+        <v>459</v>
       </c>
       <c r="D219" s="2" t="s">
         <v>460</v>
@@ -9576,7 +9585,7 @@
         <v>8</v>
       </c>
       <c r="I219" s="2" t="n">
-        <v>90.18</v>
+        <v>97.18</v>
       </c>
       <c r="J219" s="2" t="s">
         <v>8</v>
@@ -9587,10 +9596,10 @@
         <v>2021</v>
       </c>
       <c r="B220" s="2" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C220" s="2" t="s">
-        <v>418</v>
+        <v>459</v>
       </c>
       <c r="D220" s="2" t="s">
         <v>462</v>
@@ -9608,7 +9617,7 @@
         <v>8</v>
       </c>
       <c r="I220" s="2" t="n">
-        <v>89.88</v>
+        <v>96.43</v>
       </c>
       <c r="J220" s="2" t="s">
         <v>8</v>
@@ -9619,10 +9628,10 @@
         <v>2021</v>
       </c>
       <c r="B221" s="2" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C221" s="2" t="s">
-        <v>457</v>
+        <v>416</v>
       </c>
       <c r="D221" s="2" t="s">
         <v>464</v>
@@ -9640,7 +9649,7 @@
         <v>8</v>
       </c>
       <c r="I221" s="2" t="n">
-        <v>89.29</v>
+        <v>96.28</v>
       </c>
       <c r="J221" s="2" t="s">
         <v>8</v>
@@ -9672,7 +9681,7 @@
         <v>8</v>
       </c>
       <c r="I222" s="2" t="n">
-        <v>83.67</v>
+        <v>92.13</v>
       </c>
       <c r="J222" s="2" t="s">
         <v>8</v>
@@ -9704,7 +9713,7 @@
         <v>8</v>
       </c>
       <c r="I223" s="2" t="n">
-        <v>79.11</v>
+        <v>85.15</v>
       </c>
       <c r="J223" s="2" t="s">
         <v>8</v>
@@ -9718,13 +9727,13 @@
         <v>2</v>
       </c>
       <c r="C224" s="2" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="D224" s="2" t="s">
         <v>470</v>
       </c>
       <c r="E224" s="2" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="F224" s="2" t="s">
         <v>405</v>
@@ -9736,7 +9745,7 @@
         <v>8</v>
       </c>
       <c r="I224" s="2" t="n">
-        <v>75.2</v>
+        <v>80.8</v>
       </c>
       <c r="J224" s="2" t="s">
         <v>8</v>
@@ -9768,7 +9777,7 @@
         <v>8</v>
       </c>
       <c r="I225" s="2" t="n">
-        <v>73.91</v>
+        <v>78.56</v>
       </c>
       <c r="J225" s="2" t="s">
         <v>8</v>
@@ -9779,10 +9788,10 @@
         <v>2021</v>
       </c>
       <c r="B226" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C226" s="2" t="s">
-        <v>457</v>
+        <v>411</v>
       </c>
       <c r="D226" s="2" t="s">
         <v>473</v>
@@ -9800,7 +9809,7 @@
         <v>8</v>
       </c>
       <c r="I226" s="2" t="n">
-        <v>72.51</v>
+        <v>77.76</v>
       </c>
       <c r="J226" s="2" t="s">
         <v>8</v>
@@ -9811,10 +9820,10 @@
         <v>2021</v>
       </c>
       <c r="B227" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C227" s="2" t="s">
-        <v>411</v>
+        <v>459</v>
       </c>
       <c r="D227" s="2" t="s">
         <v>475</v>
@@ -9832,7 +9841,7 @@
         <v>8</v>
       </c>
       <c r="I227" s="2" t="n">
-        <v>71.43</v>
+        <v>77.34</v>
       </c>
       <c r="J227" s="2" t="s">
         <v>8</v>
@@ -9864,7 +9873,7 @@
         <v>8</v>
       </c>
       <c r="I228" s="2" t="n">
-        <v>64.6</v>
+        <v>69.67</v>
       </c>
       <c r="J228" s="2" t="s">
         <v>8</v>
@@ -9878,7 +9887,7 @@
         <v>2</v>
       </c>
       <c r="C229" s="2" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="D229" s="2" t="s">
         <v>479</v>
@@ -9896,7 +9905,7 @@
         <v>8</v>
       </c>
       <c r="I229" s="2" t="n">
-        <v>61.46</v>
+        <v>65.99</v>
       </c>
       <c r="J229" s="2" t="s">
         <v>8</v>
@@ -9928,7 +9937,7 @@
         <v>8</v>
       </c>
       <c r="I230" s="2" t="n">
-        <v>60.04</v>
+        <v>63.76</v>
       </c>
       <c r="J230" s="2" t="s">
         <v>8</v>
@@ -9942,7 +9951,7 @@
         <v>2</v>
       </c>
       <c r="C231" s="2" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="D231" s="2" t="s">
         <v>483</v>
@@ -9960,7 +9969,7 @@
         <v>8</v>
       </c>
       <c r="I231" s="2" t="n">
-        <v>57.95</v>
+        <v>61.68</v>
       </c>
       <c r="J231" s="2" t="s">
         <v>8</v>
@@ -9974,7 +9983,7 @@
         <v>2</v>
       </c>
       <c r="C232" s="2" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="D232" s="2" t="s">
         <v>485</v>
@@ -9992,7 +10001,7 @@
         <v>8</v>
       </c>
       <c r="I232" s="2" t="n">
-        <v>51.39</v>
+        <v>56.41</v>
       </c>
       <c r="J232" s="2" t="s">
         <v>8</v>
@@ -10006,7 +10015,7 @@
         <v>2</v>
       </c>
       <c r="C233" s="2" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="D233" s="2" t="s">
         <v>487</v>
@@ -10024,7 +10033,7 @@
         <v>8</v>
       </c>
       <c r="I233" s="2" t="n">
-        <v>51.16</v>
+        <v>54.75</v>
       </c>
       <c r="J233" s="2" t="s">
         <v>8</v>
@@ -10056,7 +10065,7 @@
         <v>8</v>
       </c>
       <c r="I234" s="2" t="n">
-        <v>37.46</v>
+        <v>40.04</v>
       </c>
       <c r="J234" s="2" t="s">
         <v>8</v>
@@ -10070,7 +10079,7 @@
         <v>2</v>
       </c>
       <c r="C235" s="2" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="D235" s="2" t="s">
         <v>491</v>
@@ -10088,7 +10097,7 @@
         <v>8</v>
       </c>
       <c r="I235" s="2" t="n">
-        <v>34.84</v>
+        <v>36.9</v>
       </c>
       <c r="J235" s="2" t="s">
         <v>8</v>
@@ -10120,7 +10129,7 @@
         <v>8</v>
       </c>
       <c r="I236" s="2" t="n">
-        <v>177.5</v>
+        <v>194.95</v>
       </c>
       <c r="J236" s="2" t="s">
         <v>8</v>
@@ -10152,7 +10161,7 @@
         <v>8</v>
       </c>
       <c r="I237" s="2" t="n">
-        <v>169.09</v>
+        <v>179.31</v>
       </c>
       <c r="J237" s="2" t="s">
         <v>8</v>
@@ -10184,7 +10193,7 @@
         <v>8</v>
       </c>
       <c r="I238" s="2" t="n">
-        <v>162.57</v>
+        <v>174.94</v>
       </c>
       <c r="J238" s="2" t="s">
         <v>8</v>
@@ -10216,7 +10225,7 @@
         <v>8</v>
       </c>
       <c r="I239" s="2" t="n">
-        <v>159.91</v>
+        <v>171.55</v>
       </c>
       <c r="J239" s="2" t="s">
         <v>8</v>
@@ -10227,10 +10236,10 @@
         <v>2021</v>
       </c>
       <c r="B240" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C240" s="2" t="s">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="D240" s="2" t="s">
         <v>505</v>
@@ -10248,7 +10257,7 @@
         <v>8</v>
       </c>
       <c r="I240" s="2" t="n">
-        <v>158.75</v>
+        <v>171.45</v>
       </c>
       <c r="J240" s="2" t="s">
         <v>8</v>
@@ -10280,7 +10289,7 @@
         <v>8</v>
       </c>
       <c r="I241" s="2" t="n">
-        <v>158.37</v>
+        <v>171.36</v>
       </c>
       <c r="J241" s="2" t="s">
         <v>8</v>
@@ -10291,10 +10300,10 @@
         <v>2021</v>
       </c>
       <c r="B242" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C242" s="2" t="s">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="D242" s="2" t="s">
         <v>509</v>
@@ -10312,7 +10321,7 @@
         <v>8</v>
       </c>
       <c r="I242" s="2" t="n">
-        <v>158.3</v>
+        <v>171.07</v>
       </c>
       <c r="J242" s="2" t="s">
         <v>8</v>
@@ -10344,7 +10353,7 @@
         <v>8</v>
       </c>
       <c r="I243" s="2" t="n">
-        <v>156.56</v>
+        <v>166.86</v>
       </c>
       <c r="J243" s="2" t="s">
         <v>8</v>
@@ -10376,7 +10385,7 @@
         <v>8</v>
       </c>
       <c r="I244" s="2" t="n">
-        <v>154.86</v>
+        <v>165.8</v>
       </c>
       <c r="J244" s="2" t="s">
         <v>8</v>
@@ -10408,7 +10417,7 @@
         <v>8</v>
       </c>
       <c r="I245" s="2" t="n">
-        <v>151.89</v>
+        <v>164.74</v>
       </c>
       <c r="J245" s="2" t="s">
         <v>8</v>
@@ -10419,10 +10428,10 @@
         <v>2021</v>
       </c>
       <c r="B246" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C246" s="2" t="s">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="D246" s="2" t="s">
         <v>517</v>
@@ -10440,7 +10449,7 @@
         <v>8</v>
       </c>
       <c r="I246" s="2" t="n">
-        <v>149.2</v>
+        <v>161.93</v>
       </c>
       <c r="J246" s="2" t="s">
         <v>8</v>
@@ -10451,10 +10460,10 @@
         <v>2021</v>
       </c>
       <c r="B247" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C247" s="2" t="s">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="D247" s="2" t="s">
         <v>519</v>
@@ -10472,7 +10481,7 @@
         <v>8</v>
       </c>
       <c r="I247" s="2" t="n">
-        <v>148.48</v>
+        <v>161.87</v>
       </c>
       <c r="J247" s="2" t="s">
         <v>8</v>
@@ -10504,7 +10513,7 @@
         <v>8</v>
       </c>
       <c r="I248" s="2" t="n">
-        <v>148.23</v>
+        <v>161.85</v>
       </c>
       <c r="J248" s="2" t="s">
         <v>8</v>
@@ -10536,7 +10545,7 @@
         <v>8</v>
       </c>
       <c r="I249" s="2" t="n">
-        <v>148.06</v>
+        <v>159.88</v>
       </c>
       <c r="J249" s="2" t="s">
         <v>8</v>
@@ -10547,10 +10556,10 @@
         <v>2021</v>
       </c>
       <c r="B250" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C250" s="2" t="s">
-        <v>523</v>
+        <v>493</v>
       </c>
       <c r="D250" s="2" t="s">
         <v>526</v>
@@ -10568,7 +10577,7 @@
         <v>8</v>
       </c>
       <c r="I250" s="2" t="n">
-        <v>146.03</v>
+        <v>158.39</v>
       </c>
       <c r="J250" s="2" t="s">
         <v>8</v>
@@ -10579,10 +10588,10 @@
         <v>2021</v>
       </c>
       <c r="B251" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C251" s="2" t="s">
-        <v>493</v>
+        <v>523</v>
       </c>
       <c r="D251" s="2" t="s">
         <v>528</v>
@@ -10600,7 +10609,7 @@
         <v>8</v>
       </c>
       <c r="I251" s="2" t="n">
-        <v>144.23</v>
+        <v>158.07</v>
       </c>
       <c r="J251" s="2" t="s">
         <v>8</v>
@@ -10632,7 +10641,7 @@
         <v>8</v>
       </c>
       <c r="I252" s="2" t="n">
-        <v>143</v>
+        <v>153.48</v>
       </c>
       <c r="J252" s="2" t="s">
         <v>8</v>
@@ -10643,10 +10652,10 @@
         <v>2021</v>
       </c>
       <c r="B253" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C253" s="2" t="s">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="D253" s="2" t="s">
         <v>532</v>
@@ -10664,7 +10673,7 @@
         <v>8</v>
       </c>
       <c r="I253" s="2" t="n">
-        <v>141.04</v>
+        <v>152.56</v>
       </c>
       <c r="J253" s="2" t="s">
         <v>8</v>
@@ -10675,10 +10684,10 @@
         <v>2021</v>
       </c>
       <c r="B254" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C254" s="2" t="s">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="D254" s="2" t="s">
         <v>534</v>
@@ -10696,7 +10705,7 @@
         <v>8</v>
       </c>
       <c r="I254" s="2" t="n">
-        <v>140.33</v>
+        <v>151.62</v>
       </c>
       <c r="J254" s="2" t="s">
         <v>8</v>
@@ -10707,10 +10716,10 @@
         <v>2021</v>
       </c>
       <c r="B255" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C255" s="2" t="s">
-        <v>523</v>
+        <v>498</v>
       </c>
       <c r="D255" s="2" t="s">
         <v>536</v>
@@ -10728,7 +10737,7 @@
         <v>8</v>
       </c>
       <c r="I255" s="2" t="n">
-        <v>139.83</v>
+        <v>151.31</v>
       </c>
       <c r="J255" s="2" t="s">
         <v>8</v>
@@ -10739,10 +10748,10 @@
         <v>2021</v>
       </c>
       <c r="B256" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C256" s="2" t="s">
-        <v>493</v>
+        <v>523</v>
       </c>
       <c r="D256" s="2" t="s">
         <v>538</v>
@@ -10760,7 +10769,7 @@
         <v>8</v>
       </c>
       <c r="I256" s="2" t="n">
-        <v>139.8</v>
+        <v>151.01</v>
       </c>
       <c r="J256" s="2" t="s">
         <v>8</v>
@@ -10792,7 +10801,7 @@
         <v>8</v>
       </c>
       <c r="I257" s="2" t="n">
-        <v>139.73</v>
+        <v>150.78</v>
       </c>
       <c r="J257" s="2" t="s">
         <v>8</v>
@@ -10824,7 +10833,7 @@
         <v>8</v>
       </c>
       <c r="I258" s="2" t="n">
-        <v>139.22</v>
+        <v>150.31</v>
       </c>
       <c r="J258" s="2" t="s">
         <v>8</v>
@@ -10835,10 +10844,10 @@
         <v>2021</v>
       </c>
       <c r="B259" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C259" s="2" t="s">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="D259" s="2" t="s">
         <v>544</v>
@@ -10856,7 +10865,7 @@
         <v>8</v>
       </c>
       <c r="I259" s="2" t="n">
-        <v>138.33</v>
+        <v>150.05</v>
       </c>
       <c r="J259" s="2" t="s">
         <v>8</v>
@@ -10888,7 +10897,7 @@
         <v>8</v>
       </c>
       <c r="I260" s="2" t="n">
-        <v>137.53</v>
+        <v>148.89</v>
       </c>
       <c r="J260" s="2" t="s">
         <v>8</v>
@@ -10920,7 +10929,7 @@
         <v>8</v>
       </c>
       <c r="I261" s="2" t="n">
-        <v>137.17</v>
+        <v>148.18</v>
       </c>
       <c r="J261" s="2" t="s">
         <v>8</v>
@@ -10931,10 +10940,10 @@
         <v>2021</v>
       </c>
       <c r="B262" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C262" s="2" t="s">
-        <v>523</v>
+        <v>498</v>
       </c>
       <c r="D262" s="2" t="s">
         <v>550</v>
@@ -10952,7 +10961,7 @@
         <v>8</v>
       </c>
       <c r="I262" s="2" t="n">
-        <v>137.04</v>
+        <v>147.91</v>
       </c>
       <c r="J262" s="2" t="s">
         <v>8</v>
@@ -10963,10 +10972,10 @@
         <v>2021</v>
       </c>
       <c r="B263" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C263" s="2" t="s">
-        <v>498</v>
+        <v>523</v>
       </c>
       <c r="D263" s="2" t="s">
         <v>552</v>
@@ -10984,7 +10993,7 @@
         <v>8</v>
       </c>
       <c r="I263" s="2" t="n">
-        <v>136.99</v>
+        <v>147.73</v>
       </c>
       <c r="J263" s="2" t="s">
         <v>8</v>
@@ -11016,7 +11025,7 @@
         <v>8</v>
       </c>
       <c r="I264" s="2" t="n">
-        <v>136.79</v>
+        <v>147.46</v>
       </c>
       <c r="J264" s="2" t="s">
         <v>8</v>
@@ -11048,7 +11057,7 @@
         <v>8</v>
       </c>
       <c r="I265" s="2" t="n">
-        <v>136.5</v>
+        <v>147.26</v>
       </c>
       <c r="J265" s="2" t="s">
         <v>8</v>
@@ -11080,7 +11089,7 @@
         <v>8</v>
       </c>
       <c r="I266" s="2" t="n">
-        <v>134.3</v>
+        <v>145.05</v>
       </c>
       <c r="J266" s="2" t="s">
         <v>8</v>
@@ -11112,7 +11121,7 @@
         <v>8</v>
       </c>
       <c r="I267" s="2" t="n">
-        <v>132.84</v>
+        <v>144.1</v>
       </c>
       <c r="J267" s="2" t="s">
         <v>8</v>
@@ -11144,7 +11153,7 @@
         <v>8</v>
       </c>
       <c r="I268" s="2" t="n">
-        <v>132.3</v>
+        <v>144.05</v>
       </c>
       <c r="J268" s="2" t="s">
         <v>8</v>
@@ -11176,7 +11185,7 @@
         <v>8</v>
       </c>
       <c r="I269" s="2" t="n">
-        <v>131.5</v>
+        <v>142.62</v>
       </c>
       <c r="J269" s="2" t="s">
         <v>8</v>
@@ -11187,10 +11196,10 @@
         <v>2021</v>
       </c>
       <c r="B270" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C270" s="2" t="s">
-        <v>523</v>
+        <v>493</v>
       </c>
       <c r="D270" s="2" t="s">
         <v>567</v>
@@ -11208,7 +11217,7 @@
         <v>8</v>
       </c>
       <c r="I270" s="2" t="n">
-        <v>131.19</v>
+        <v>141.79</v>
       </c>
       <c r="J270" s="2" t="s">
         <v>8</v>
@@ -11219,10 +11228,10 @@
         <v>2021</v>
       </c>
       <c r="B271" s="2" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C271" s="2" t="s">
-        <v>493</v>
+        <v>556</v>
       </c>
       <c r="D271" s="2" t="s">
         <v>569</v>
@@ -11240,7 +11249,7 @@
         <v>8</v>
       </c>
       <c r="I271" s="2" t="n">
-        <v>130.34</v>
+        <v>141.23</v>
       </c>
       <c r="J271" s="2" t="s">
         <v>8</v>
@@ -11251,10 +11260,10 @@
         <v>2021</v>
       </c>
       <c r="B272" s="2" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C272" s="2" t="s">
-        <v>556</v>
+        <v>523</v>
       </c>
       <c r="D272" s="2" t="s">
         <v>571</v>
@@ -11272,7 +11281,7 @@
         <v>8</v>
       </c>
       <c r="I272" s="2" t="n">
-        <v>129.74</v>
+        <v>140.81</v>
       </c>
       <c r="J272" s="2" t="s">
         <v>8</v>
@@ -11283,10 +11292,10 @@
         <v>2021</v>
       </c>
       <c r="B273" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C273" s="2" t="s">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="D273" s="2" t="s">
         <v>573</v>
@@ -11304,7 +11313,7 @@
         <v>8</v>
       </c>
       <c r="I273" s="2" t="n">
-        <v>129.51</v>
+        <v>140.32</v>
       </c>
       <c r="J273" s="2" t="s">
         <v>8</v>
@@ -11315,10 +11324,10 @@
         <v>2021</v>
       </c>
       <c r="B274" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C274" s="2" t="s">
-        <v>523</v>
+        <v>493</v>
       </c>
       <c r="D274" s="2" t="s">
         <v>575</v>
@@ -11336,7 +11345,7 @@
         <v>8</v>
       </c>
       <c r="I274" s="2" t="n">
-        <v>129.22</v>
+        <v>139.94</v>
       </c>
       <c r="J274" s="2" t="s">
         <v>8</v>
@@ -11368,7 +11377,7 @@
         <v>8</v>
       </c>
       <c r="I275" s="2" t="n">
-        <v>129.15</v>
+        <v>139.08</v>
       </c>
       <c r="J275" s="2" t="s">
         <v>8</v>
@@ -11400,7 +11409,7 @@
         <v>8</v>
       </c>
       <c r="I276" s="2" t="n">
-        <v>128.86</v>
+        <v>139.05</v>
       </c>
       <c r="J276" s="2" t="s">
         <v>8</v>
@@ -11432,7 +11441,7 @@
         <v>8</v>
       </c>
       <c r="I277" s="2" t="n">
-        <v>127.78</v>
+        <v>138.57</v>
       </c>
       <c r="J277" s="2" t="s">
         <v>8</v>
@@ -11443,10 +11452,10 @@
         <v>2021</v>
       </c>
       <c r="B278" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C278" s="2" t="s">
-        <v>498</v>
+        <v>523</v>
       </c>
       <c r="D278" s="2" t="s">
         <v>583</v>
@@ -11464,7 +11473,7 @@
         <v>8</v>
       </c>
       <c r="I278" s="2" t="n">
-        <v>127.59</v>
+        <v>138.28</v>
       </c>
       <c r="J278" s="2" t="s">
         <v>8</v>
@@ -11475,10 +11484,10 @@
         <v>2021</v>
       </c>
       <c r="B279" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C279" s="2" t="s">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="D279" s="2" t="s">
         <v>585</v>
@@ -11496,7 +11505,7 @@
         <v>8</v>
       </c>
       <c r="I279" s="2" t="n">
-        <v>127.25</v>
+        <v>137.05</v>
       </c>
       <c r="J279" s="2" t="s">
         <v>8</v>
@@ -11507,10 +11516,10 @@
         <v>2021</v>
       </c>
       <c r="B280" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C280" s="2" t="s">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="D280" s="2" t="s">
         <v>587</v>
@@ -11528,7 +11537,7 @@
         <v>8</v>
       </c>
       <c r="I280" s="2" t="n">
-        <v>124.9</v>
+        <v>136.11</v>
       </c>
       <c r="J280" s="2" t="s">
         <v>8</v>
@@ -11560,7 +11569,7 @@
         <v>8</v>
       </c>
       <c r="I281" s="2" t="n">
-        <v>124.37</v>
+        <v>135.08</v>
       </c>
       <c r="J281" s="2" t="s">
         <v>8</v>
@@ -11571,10 +11580,10 @@
         <v>2021</v>
       </c>
       <c r="B282" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C282" s="2" t="s">
-        <v>493</v>
+        <v>523</v>
       </c>
       <c r="D282" s="2" t="s">
         <v>591</v>
@@ -11592,7 +11601,7 @@
         <v>8</v>
       </c>
       <c r="I282" s="2" t="n">
-        <v>124.36</v>
+        <v>134.03</v>
       </c>
       <c r="J282" s="2" t="s">
         <v>8</v>
@@ -11603,10 +11612,10 @@
         <v>2021</v>
       </c>
       <c r="B283" s="2" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C283" s="2" t="s">
-        <v>556</v>
+        <v>493</v>
       </c>
       <c r="D283" s="2" t="s">
         <v>593</v>
@@ -11624,7 +11633,7 @@
         <v>8</v>
       </c>
       <c r="I283" s="2" t="n">
-        <v>124.18</v>
+        <v>133.95</v>
       </c>
       <c r="J283" s="2" t="s">
         <v>8</v>
@@ -11635,10 +11644,10 @@
         <v>2021</v>
       </c>
       <c r="B284" s="2" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C284" s="2" t="s">
-        <v>523</v>
+        <v>556</v>
       </c>
       <c r="D284" s="2" t="s">
         <v>595</v>
@@ -11656,7 +11665,7 @@
         <v>8</v>
       </c>
       <c r="I284" s="2" t="n">
-        <v>124.01</v>
+        <v>133.8</v>
       </c>
       <c r="J284" s="2" t="s">
         <v>8</v>
@@ -11667,10 +11676,10 @@
         <v>2021</v>
       </c>
       <c r="B285" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C285" s="2" t="s">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="D285" s="2" t="s">
         <v>597</v>
@@ -11688,7 +11697,7 @@
         <v>8</v>
       </c>
       <c r="I285" s="2" t="n">
-        <v>123.26</v>
+        <v>133.36</v>
       </c>
       <c r="J285" s="2" t="s">
         <v>8</v>
@@ -11699,10 +11708,10 @@
         <v>2021</v>
       </c>
       <c r="B286" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C286" s="2" t="s">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="D286" s="2" t="s">
         <v>599</v>
@@ -11720,7 +11729,7 @@
         <v>8</v>
       </c>
       <c r="I286" s="2" t="n">
-        <v>123.07</v>
+        <v>133.05</v>
       </c>
       <c r="J286" s="2" t="s">
         <v>8</v>
@@ -11752,7 +11761,7 @@
         <v>8</v>
       </c>
       <c r="I287" s="2" t="n">
-        <v>122.81</v>
+        <v>132.67</v>
       </c>
       <c r="J287" s="2" t="s">
         <v>8</v>
@@ -11784,7 +11793,7 @@
         <v>8</v>
       </c>
       <c r="I288" s="2" t="n">
-        <v>122.62</v>
+        <v>132.33</v>
       </c>
       <c r="J288" s="2" t="s">
         <v>8</v>
@@ -11795,10 +11804,10 @@
         <v>2021</v>
       </c>
       <c r="B289" s="2" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C289" s="2" t="s">
-        <v>556</v>
+        <v>498</v>
       </c>
       <c r="D289" s="2" t="s">
         <v>605</v>
@@ -11816,7 +11825,7 @@
         <v>8</v>
       </c>
       <c r="I289" s="2" t="n">
-        <v>122</v>
+        <v>132.2</v>
       </c>
       <c r="J289" s="2" t="s">
         <v>8</v>
@@ -11827,10 +11836,10 @@
         <v>2021</v>
       </c>
       <c r="B290" s="2" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C290" s="2" t="s">
-        <v>498</v>
+        <v>556</v>
       </c>
       <c r="D290" s="2" t="s">
         <v>607</v>
@@ -11848,7 +11857,7 @@
         <v>8</v>
       </c>
       <c r="I290" s="2" t="n">
-        <v>121.66</v>
+        <v>131.83</v>
       </c>
       <c r="J290" s="2" t="s">
         <v>8</v>
@@ -11859,10 +11868,10 @@
         <v>2021</v>
       </c>
       <c r="B291" s="2" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C291" s="2" t="s">
-        <v>556</v>
+        <v>498</v>
       </c>
       <c r="D291" s="2" t="s">
         <v>609</v>
@@ -11880,7 +11889,7 @@
         <v>8</v>
       </c>
       <c r="I291" s="2" t="n">
-        <v>121.46</v>
+        <v>130.86</v>
       </c>
       <c r="J291" s="2" t="s">
         <v>8</v>
@@ -11891,10 +11900,10 @@
         <v>2021</v>
       </c>
       <c r="B292" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C292" s="2" t="s">
-        <v>498</v>
+        <v>523</v>
       </c>
       <c r="D292" s="2" t="s">
         <v>611</v>
@@ -11912,7 +11921,7 @@
         <v>8</v>
       </c>
       <c r="I292" s="2" t="n">
-        <v>121</v>
+        <v>130.63</v>
       </c>
       <c r="J292" s="2" t="s">
         <v>8</v>
@@ -11923,10 +11932,10 @@
         <v>2021</v>
       </c>
       <c r="B293" s="2" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C293" s="2" t="s">
-        <v>523</v>
+        <v>556</v>
       </c>
       <c r="D293" s="2" t="s">
         <v>613</v>
@@ -11944,7 +11953,7 @@
         <v>8</v>
       </c>
       <c r="I293" s="2" t="n">
-        <v>119.99</v>
+        <v>130.45</v>
       </c>
       <c r="J293" s="2" t="s">
         <v>8</v>
@@ -11976,7 +11985,7 @@
         <v>8</v>
       </c>
       <c r="I294" s="2" t="n">
-        <v>119.07</v>
+        <v>128.61</v>
       </c>
       <c r="J294" s="2" t="s">
         <v>8</v>
@@ -12008,7 +12017,7 @@
         <v>8</v>
       </c>
       <c r="I295" s="2" t="n">
-        <v>118.81</v>
+        <v>128.33</v>
       </c>
       <c r="J295" s="2" t="s">
         <v>8</v>
@@ -12040,7 +12049,7 @@
         <v>8</v>
       </c>
       <c r="I296" s="2" t="n">
-        <v>117.12</v>
+        <v>126.62</v>
       </c>
       <c r="J296" s="2" t="s">
         <v>8</v>
@@ -12051,10 +12060,10 @@
         <v>2021</v>
       </c>
       <c r="B297" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C297" s="2" t="s">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="D297" s="2" t="s">
         <v>621</v>
@@ -12072,7 +12081,7 @@
         <v>8</v>
       </c>
       <c r="I297" s="2" t="n">
-        <v>115.48</v>
+        <v>124.31</v>
       </c>
       <c r="J297" s="2" t="s">
         <v>8</v>
@@ -12083,10 +12092,10 @@
         <v>2021</v>
       </c>
       <c r="B298" s="2" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C298" s="2" t="s">
-        <v>493</v>
+        <v>556</v>
       </c>
       <c r="D298" s="2" t="s">
         <v>623</v>
@@ -12104,7 +12113,7 @@
         <v>8</v>
       </c>
       <c r="I298" s="2" t="n">
-        <v>115.25</v>
+        <v>123.93</v>
       </c>
       <c r="J298" s="2" t="s">
         <v>8</v>
@@ -12115,10 +12124,10 @@
         <v>2021</v>
       </c>
       <c r="B299" s="2" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C299" s="2" t="s">
-        <v>556</v>
+        <v>498</v>
       </c>
       <c r="D299" s="2" t="s">
         <v>625</v>
@@ -12136,7 +12145,7 @@
         <v>8</v>
       </c>
       <c r="I299" s="2" t="n">
-        <v>115.04</v>
+        <v>123.67</v>
       </c>
       <c r="J299" s="2" t="s">
         <v>8</v>
@@ -12147,10 +12156,10 @@
         <v>2021</v>
       </c>
       <c r="B300" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C300" s="2" t="s">
-        <v>523</v>
+        <v>498</v>
       </c>
       <c r="D300" s="2" t="s">
         <v>627</v>
@@ -12168,7 +12177,7 @@
         <v>8</v>
       </c>
       <c r="I300" s="2" t="n">
-        <v>113.37</v>
+        <v>123.65</v>
       </c>
       <c r="J300" s="2" t="s">
         <v>8</v>
@@ -12179,10 +12188,10 @@
         <v>2021</v>
       </c>
       <c r="B301" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C301" s="2" t="s">
-        <v>498</v>
+        <v>523</v>
       </c>
       <c r="D301" s="2" t="s">
         <v>629</v>
@@ -12200,7 +12209,7 @@
         <v>8</v>
       </c>
       <c r="I301" s="2" t="n">
-        <v>113.2</v>
+        <v>122.65</v>
       </c>
       <c r="J301" s="2" t="s">
         <v>8</v>
@@ -12211,16 +12220,16 @@
         <v>2021</v>
       </c>
       <c r="B302" s="2" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C302" s="2" t="s">
-        <v>556</v>
+        <v>493</v>
       </c>
       <c r="D302" s="2" t="s">
         <v>631</v>
       </c>
       <c r="E302" s="2" t="s">
-        <v>493</v>
+        <v>632</v>
       </c>
       <c r="F302" s="2" t="s">
         <v>496</v>
@@ -12232,7 +12241,7 @@
         <v>8</v>
       </c>
       <c r="I302" s="2" t="n">
-        <v>112.08</v>
+        <v>121.33</v>
       </c>
       <c r="J302" s="2" t="s">
         <v>8</v>
@@ -12243,16 +12252,16 @@
         <v>2021</v>
       </c>
       <c r="B303" s="2" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C303" s="2" t="s">
-        <v>523</v>
+        <v>556</v>
       </c>
       <c r="D303" s="2" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="E303" s="2" t="s">
-        <v>633</v>
+        <v>493</v>
       </c>
       <c r="F303" s="2" t="s">
         <v>496</v>
@@ -12264,7 +12273,7 @@
         <v>8</v>
       </c>
       <c r="I303" s="2" t="n">
-        <v>111.29</v>
+        <v>120.3</v>
       </c>
       <c r="J303" s="2" t="s">
         <v>8</v>
@@ -12275,10 +12284,10 @@
         <v>2021</v>
       </c>
       <c r="B304" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C304" s="2" t="s">
-        <v>493</v>
+        <v>523</v>
       </c>
       <c r="D304" s="2" t="s">
         <v>634</v>
@@ -12296,7 +12305,7 @@
         <v>8</v>
       </c>
       <c r="I304" s="2" t="n">
-        <v>111.26</v>
+        <v>120.19</v>
       </c>
       <c r="J304" s="2" t="s">
         <v>8</v>
@@ -12328,7 +12337,7 @@
         <v>8</v>
       </c>
       <c r="I305" s="2" t="n">
-        <v>111.01</v>
+        <v>120.11</v>
       </c>
       <c r="J305" s="2" t="s">
         <v>8</v>
@@ -12360,7 +12369,7 @@
         <v>8</v>
       </c>
       <c r="I306" s="2" t="n">
-        <v>110.16</v>
+        <v>119.66</v>
       </c>
       <c r="J306" s="2" t="s">
         <v>8</v>
@@ -12371,10 +12380,10 @@
         <v>2021</v>
       </c>
       <c r="B307" s="2" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C307" s="2" t="s">
-        <v>523</v>
+        <v>556</v>
       </c>
       <c r="D307" s="2" t="s">
         <v>640</v>
@@ -12392,7 +12401,7 @@
         <v>8</v>
       </c>
       <c r="I307" s="2" t="n">
-        <v>108.1</v>
+        <v>116.62</v>
       </c>
       <c r="J307" s="2" t="s">
         <v>8</v>
@@ -12403,10 +12412,10 @@
         <v>2021</v>
       </c>
       <c r="B308" s="2" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C308" s="2" t="s">
-        <v>556</v>
+        <v>523</v>
       </c>
       <c r="D308" s="2" t="s">
         <v>642</v>
@@ -12424,7 +12433,7 @@
         <v>8</v>
       </c>
       <c r="I308" s="2" t="n">
-        <v>107.98</v>
+        <v>116.33</v>
       </c>
       <c r="J308" s="2" t="s">
         <v>8</v>
@@ -12456,7 +12465,7 @@
         <v>8</v>
       </c>
       <c r="I309" s="2" t="n">
-        <v>106.71</v>
+        <v>115.05</v>
       </c>
       <c r="J309" s="2" t="s">
         <v>8</v>
@@ -12488,7 +12497,7 @@
         <v>8</v>
       </c>
       <c r="I310" s="2" t="n">
-        <v>104.66</v>
+        <v>113.08</v>
       </c>
       <c r="J310" s="2" t="s">
         <v>8</v>
@@ -12499,10 +12508,10 @@
         <v>2021</v>
       </c>
       <c r="B311" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C311" s="2" t="s">
-        <v>523</v>
+        <v>498</v>
       </c>
       <c r="D311" s="2" t="s">
         <v>648</v>
@@ -12520,7 +12529,7 @@
         <v>8</v>
       </c>
       <c r="I311" s="2" t="n">
-        <v>104.34</v>
+        <v>112.43</v>
       </c>
       <c r="J311" s="2" t="s">
         <v>8</v>
@@ -12531,10 +12540,10 @@
         <v>2021</v>
       </c>
       <c r="B312" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C312" s="2" t="s">
-        <v>498</v>
+        <v>523</v>
       </c>
       <c r="D312" s="2" t="s">
         <v>650</v>
@@ -12552,7 +12561,7 @@
         <v>8</v>
       </c>
       <c r="I312" s="2" t="n">
-        <v>103.38</v>
+        <v>112.04</v>
       </c>
       <c r="J312" s="2" t="s">
         <v>8</v>
@@ -12584,7 +12593,7 @@
         <v>8</v>
       </c>
       <c r="I313" s="2" t="n">
-        <v>103.07</v>
+        <v>111.63</v>
       </c>
       <c r="J313" s="2" t="s">
         <v>8</v>
@@ -12616,7 +12625,7 @@
         <v>8</v>
       </c>
       <c r="I314" s="2" t="n">
-        <v>103.03</v>
+        <v>111.11</v>
       </c>
       <c r="J314" s="2" t="s">
         <v>8</v>
@@ -12627,10 +12636,10 @@
         <v>2021</v>
       </c>
       <c r="B315" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C315" s="2" t="s">
-        <v>523</v>
+        <v>493</v>
       </c>
       <c r="D315" s="2" t="s">
         <v>656</v>
@@ -12648,7 +12657,7 @@
         <v>8</v>
       </c>
       <c r="I315" s="2" t="n">
-        <v>101.19</v>
+        <v>107.7</v>
       </c>
       <c r="J315" s="2" t="s">
         <v>8</v>
@@ -12659,10 +12668,10 @@
         <v>2021</v>
       </c>
       <c r="B316" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C316" s="2" t="s">
-        <v>493</v>
+        <v>523</v>
       </c>
       <c r="D316" s="2" t="s">
         <v>658</v>
@@ -12680,7 +12689,7 @@
         <v>8</v>
       </c>
       <c r="I316" s="2" t="n">
-        <v>100.28</v>
+        <v>107.59</v>
       </c>
       <c r="J316" s="2" t="s">
         <v>8</v>
@@ -12712,7 +12721,7 @@
         <v>8</v>
       </c>
       <c r="I317" s="2" t="n">
-        <v>100.25</v>
+        <v>107.39</v>
       </c>
       <c r="J317" s="2" t="s">
         <v>8</v>
@@ -12723,10 +12732,10 @@
         <v>2021</v>
       </c>
       <c r="B318" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C318" s="2" t="s">
-        <v>523</v>
+        <v>493</v>
       </c>
       <c r="D318" s="2" t="s">
         <v>662</v>
@@ -12744,7 +12753,7 @@
         <v>8</v>
       </c>
       <c r="I318" s="2" t="n">
-        <v>98.97</v>
+        <v>107.2</v>
       </c>
       <c r="J318" s="2" t="s">
         <v>8</v>
@@ -12755,10 +12764,10 @@
         <v>2021</v>
       </c>
       <c r="B319" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C319" s="2" t="s">
-        <v>493</v>
+        <v>523</v>
       </c>
       <c r="D319" s="2" t="s">
         <v>664</v>
@@ -12776,7 +12785,7 @@
         <v>8</v>
       </c>
       <c r="I319" s="2" t="n">
-        <v>98.81</v>
+        <v>105.36</v>
       </c>
       <c r="J319" s="2" t="s">
         <v>8</v>
@@ -12808,7 +12817,7 @@
         <v>8</v>
       </c>
       <c r="I320" s="2" t="n">
-        <v>97.88</v>
+        <v>105.17</v>
       </c>
       <c r="J320" s="2" t="s">
         <v>8</v>
@@ -12819,10 +12828,10 @@
         <v>2021</v>
       </c>
       <c r="B321" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C321" s="2" t="s">
-        <v>523</v>
+        <v>498</v>
       </c>
       <c r="D321" s="2" t="s">
         <v>668</v>
@@ -12840,7 +12849,7 @@
         <v>8</v>
       </c>
       <c r="I321" s="2" t="n">
-        <v>97.84</v>
+        <v>104.85</v>
       </c>
       <c r="J321" s="2" t="s">
         <v>8</v>
@@ -12872,7 +12881,7 @@
         <v>8</v>
       </c>
       <c r="I322" s="2" t="n">
-        <v>97.66</v>
+        <v>104.71</v>
       </c>
       <c r="J322" s="2" t="s">
         <v>8</v>
@@ -12883,10 +12892,10 @@
         <v>2021</v>
       </c>
       <c r="B323" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C323" s="2" t="s">
-        <v>498</v>
+        <v>523</v>
       </c>
       <c r="D323" s="2" t="s">
         <v>672</v>
@@ -12904,7 +12913,7 @@
         <v>8</v>
       </c>
       <c r="I323" s="2" t="n">
-        <v>97.3</v>
+        <v>104.33</v>
       </c>
       <c r="J323" s="2" t="s">
         <v>8</v>
@@ -12915,10 +12924,10 @@
         <v>2021</v>
       </c>
       <c r="B324" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C324" s="2" t="s">
-        <v>523</v>
+        <v>498</v>
       </c>
       <c r="D324" s="2" t="s">
         <v>674</v>
@@ -12936,7 +12945,7 @@
         <v>8</v>
       </c>
       <c r="I324" s="2" t="n">
-        <v>96.68</v>
+        <v>104.12</v>
       </c>
       <c r="J324" s="2" t="s">
         <v>8</v>
@@ -12947,10 +12956,10 @@
         <v>2021</v>
       </c>
       <c r="B325" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C325" s="2" t="s">
-        <v>498</v>
+        <v>523</v>
       </c>
       <c r="D325" s="2" t="s">
         <v>676</v>
@@ -12968,7 +12977,7 @@
         <v>8</v>
       </c>
       <c r="I325" s="2" t="n">
-        <v>96.52</v>
+        <v>104.1</v>
       </c>
       <c r="J325" s="2" t="s">
         <v>8</v>
@@ -13000,7 +13009,7 @@
         <v>8</v>
       </c>
       <c r="I326" s="2" t="n">
-        <v>95.5</v>
+        <v>103.1</v>
       </c>
       <c r="J326" s="2" t="s">
         <v>8</v>
@@ -13032,7 +13041,7 @@
         <v>8</v>
       </c>
       <c r="I327" s="2" t="n">
-        <v>94.93</v>
+        <v>102.67</v>
       </c>
       <c r="J327" s="2" t="s">
         <v>8</v>
@@ -13064,7 +13073,7 @@
         <v>8</v>
       </c>
       <c r="I328" s="2" t="n">
-        <v>94.75</v>
+        <v>101.31</v>
       </c>
       <c r="J328" s="2" t="s">
         <v>8</v>
@@ -13096,7 +13105,7 @@
         <v>8</v>
       </c>
       <c r="I329" s="2" t="n">
-        <v>93.54</v>
+        <v>101.12</v>
       </c>
       <c r="J329" s="2" t="s">
         <v>8</v>
@@ -13128,7 +13137,7 @@
         <v>8</v>
       </c>
       <c r="I330" s="2" t="n">
-        <v>93.13</v>
+        <v>100.45</v>
       </c>
       <c r="J330" s="2" t="s">
         <v>8</v>
@@ -13160,7 +13169,7 @@
         <v>8</v>
       </c>
       <c r="I331" s="2" t="n">
-        <v>92.14</v>
+        <v>99.78</v>
       </c>
       <c r="J331" s="2" t="s">
         <v>8</v>
@@ -13192,7 +13201,7 @@
         <v>8</v>
       </c>
       <c r="I332" s="2" t="n">
-        <v>86.54</v>
+        <v>93.31</v>
       </c>
       <c r="J332" s="2" t="s">
         <v>8</v>
@@ -13224,7 +13233,7 @@
         <v>8</v>
       </c>
       <c r="I333" s="2" t="n">
-        <v>86.46</v>
+        <v>92.83</v>
       </c>
       <c r="J333" s="2" t="s">
         <v>8</v>
@@ -13256,7 +13265,7 @@
         <v>8</v>
       </c>
       <c r="I334" s="2" t="n">
-        <v>84.72</v>
+        <v>91.65</v>
       </c>
       <c r="J334" s="2" t="s">
         <v>8</v>
@@ -13267,10 +13276,10 @@
         <v>2021</v>
       </c>
       <c r="B335" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C335" s="2" t="s">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="D335" s="2" t="s">
         <v>696</v>
@@ -13288,7 +13297,7 @@
         <v>8</v>
       </c>
       <c r="I335" s="2" t="n">
-        <v>84.32</v>
+        <v>90.86</v>
       </c>
       <c r="J335" s="2" t="s">
         <v>8</v>
@@ -13299,10 +13308,10 @@
         <v>2021</v>
       </c>
       <c r="B336" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C336" s="2" t="s">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="D336" s="2" t="s">
         <v>698</v>
@@ -13320,7 +13329,7 @@
         <v>8</v>
       </c>
       <c r="I336" s="2" t="n">
-        <v>84.2</v>
+        <v>90.72</v>
       </c>
       <c r="J336" s="2" t="s">
         <v>8</v>
@@ -13352,7 +13361,7 @@
         <v>8</v>
       </c>
       <c r="I337" s="2" t="n">
-        <v>77.31</v>
+        <v>83.25</v>
       </c>
       <c r="J337" s="2" t="s">
         <v>8</v>
@@ -13384,7 +13393,7 @@
         <v>8</v>
       </c>
       <c r="I338" s="2" t="n">
-        <v>76.07</v>
+        <v>82.16</v>
       </c>
       <c r="J338" s="2" t="s">
         <v>8</v>
@@ -13416,7 +13425,7 @@
         <v>8</v>
       </c>
       <c r="I339" s="2" t="n">
-        <v>74.92</v>
+        <v>80.53</v>
       </c>
       <c r="J339" s="2" t="s">
         <v>8</v>
@@ -13448,7 +13457,7 @@
         <v>8</v>
       </c>
       <c r="I340" s="2" t="n">
-        <v>67.52</v>
+        <v>72.95</v>
       </c>
       <c r="J340" s="2" t="s">
         <v>8</v>
@@ -13459,10 +13468,10 @@
         <v>2021</v>
       </c>
       <c r="B341" s="2" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C341" s="2" t="s">
-        <v>556</v>
+        <v>498</v>
       </c>
       <c r="D341" s="2" t="s">
         <v>708</v>
@@ -13480,7 +13489,7 @@
         <v>8</v>
       </c>
       <c r="I341" s="2" t="n">
-        <v>58.29</v>
+        <v>61.98</v>
       </c>
       <c r="J341" s="2" t="s">
         <v>8</v>
@@ -13491,10 +13500,10 @@
         <v>2021</v>
       </c>
       <c r="B342" s="2" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C342" s="2" t="s">
-        <v>498</v>
+        <v>556</v>
       </c>
       <c r="D342" s="2" t="s">
         <v>710</v>
@@ -13512,7 +13521,7 @@
         <v>8</v>
       </c>
       <c r="I342" s="2" t="n">
-        <v>56.67</v>
+        <v>60.93</v>
       </c>
       <c r="J342" s="2" t="s">
         <v>8</v>
@@ -13571,23 +13580,23 @@
         <v>719</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>718</v>
+        <v>722</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>718</v>
+        <v>724</v>
       </c>
     </row>
   </sheetData>
@@ -13609,21 +13618,21 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>722</v>
+        <v>725</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>723</v>
+        <v>726</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>724</v>
+        <v>727</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>725</v>
+        <v>728</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>8</v>
@@ -13632,7 +13641,7 @@
         <v>2021</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>726</v>
+        <v>729</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_nacionales/plot_nacional_d_enveje_a_2021.xlsx
+++ b/output/graficos_nacionales/plot_nacional_d_enveje_a_2021.xlsx
@@ -2161,7 +2161,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-04 19:41</t>
+    <t xml:space="preserve">2026-09-07 12:41</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_nacionales/plot_nacional_d_enveje_a_2021.xlsx
+++ b/output/graficos_nacionales/plot_nacional_d_enveje_a_2021.xlsx
@@ -2161,7 +2161,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-07 12:41</t>
+    <t xml:space="preserve">2026-09-08 10:12</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
